--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -27,10 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="54">
-  <si>
-    <t>#</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="47">
   <si>
     <t>ID</t>
   </si>
@@ -95,33 +92,6 @@
     <t>掉落金币</t>
   </si>
   <si>
-    <t>经验基础</t>
-  </si>
-  <si>
-    <t>属性基础</t>
-  </si>
-  <si>
-    <t>属性倍率</t>
-  </si>
-  <si>
-    <t>攻击倍率</t>
-  </si>
-  <si>
-    <t>防御倍率</t>
-  </si>
-  <si>
-    <t>血量倍率</t>
-  </si>
-  <si>
-    <t>Strong</t>
-  </si>
-  <si>
-    <t>Parry</t>
-  </si>
-  <si>
-    <t>DamageMul</t>
-  </si>
-  <si>
     <t>Id</t>
   </si>
   <si>
@@ -161,7 +131,16 @@
     <t>三头巨鳄</t>
   </si>
   <si>
+    <t>1E+8</t>
+  </si>
+  <si>
     <t>腐尸君主</t>
+  </si>
+  <si>
+    <t>2E+6</t>
+  </si>
+  <si>
+    <t>1E+11</t>
   </si>
   <si>
     <t>梦魇鹿神</t>
@@ -831,6 +810,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1150,7 +1130,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AF18"/>
+  <dimension ref="A1:W18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1167,25 +1147,19 @@
     <col min="12" max="12" width="11.1666666666667" style="2" customWidth="1"/>
     <col min="13" max="13" width="10" style="2" customWidth="1"/>
     <col min="14" max="14" width="10.25" style="2" customWidth="1"/>
-    <col min="15" max="15" width="5.66666666666667" style="2" customWidth="1"/>
-    <col min="16" max="16" width="6.83333333333333" style="2" customWidth="1"/>
-    <col min="17" max="17" width="8.75" style="2" customWidth="1"/>
+    <col min="15" max="15" width="8.08333333333333" style="2" customWidth="1"/>
+    <col min="16" max="16" width="9.91666666666667" style="2" customWidth="1"/>
+    <col min="17" max="17" width="10.75" style="2" customWidth="1"/>
     <col min="18" max="18" width="7.5" style="2" customWidth="1"/>
     <col min="19" max="19" width="8.75" style="2" customWidth="1"/>
     <col min="20" max="20" width="7.50833333333333" style="2" customWidth="1"/>
     <col min="21" max="21" width="8.33333333333333" style="2" customWidth="1"/>
     <col min="22" max="22" width="11.6666666666667" style="2" customWidth="1"/>
     <col min="23" max="23" width="11.1666666666667" style="2" customWidth="1"/>
-    <col min="24" max="26" width="9" style="2"/>
-    <col min="27" max="28" width="7.16666666666667" style="2" customWidth="1"/>
-    <col min="29" max="29" width="8.41666666666667" style="2" customWidth="1"/>
-    <col min="30" max="30" width="6.08333333333333" style="2" customWidth="1"/>
-    <col min="31" max="31" width="2.91666666666667" style="2" customWidth="1"/>
-    <col min="32" max="32" width="5.33333333333333" style="2" customWidth="1"/>
-    <col min="33" max="16384" width="9" style="2"/>
+    <col min="24" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:32">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="H1" s="3"/>
@@ -1204,35 +1178,8 @@
       <c r="U1" s="2"/>
       <c r="V1" s="2"/>
       <c r="W1" s="2"/>
-      <c r="X1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="AB1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>0</v>
-      </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:32">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="I2" s="2"/>
@@ -1250,289 +1197,209 @@
       <c r="U2" s="2"/>
       <c r="V2" s="2"/>
       <c r="W2" s="2"/>
-      <c r="X2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF2" s="1" t="s">
-        <v>0</v>
-      </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:32">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="J3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="K3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="L3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="M3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="N3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="O3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="P3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="Q3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="R3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="R3" s="4" t="s">
+      <c r="S3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="4" t="s">
+      <c r="T3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="T3" s="4" t="s">
+      <c r="U3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="U3" s="4" t="s">
+      <c r="V3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="V3" s="4" t="s">
+      <c r="W3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="W3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="AD3" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="AE3" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="AF3" s="4" t="s">
-        <v>30</v>
-      </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:32">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="4" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="K4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="M4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="N4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="O4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="P4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="P4" s="4" t="s">
+      <c r="Q4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="Q4" s="4" t="s">
+      <c r="R4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="R4" s="4" t="s">
+      <c r="S4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="S4" s="4" t="s">
+      <c r="T4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="T4" s="4" t="s">
+      <c r="U4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="U4" s="4" t="s">
-        <v>19</v>
-      </c>
       <c r="V4" s="4" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="W4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="Z4" s="2"/>
-      <c r="AA4" s="2"/>
-      <c r="AB4" s="2"/>
-      <c r="AC4" s="2"/>
-      <c r="AD4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="AE4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="AF4" s="4" t="s">
-        <v>30</v>
-      </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:32">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="Z5" s="2"/>
-      <c r="AA5" s="2"/>
-      <c r="AB5" s="2"/>
-      <c r="AC5" s="2"/>
-      <c r="AD5" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="AE5" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="AF5" s="4" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:32">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1543,43 +1410,37 @@
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
       </c>
       <c r="H6" s="1">
-        <v>5</v>
+        <v>10000</v>
       </c>
       <c r="I6" s="1">
-        <f t="shared" ref="I6:I45" si="0">Y6*Z6/2</f>
+        <v>10000</v>
+      </c>
+      <c r="J6" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="K6" s="1">
         <v>50</v>
       </c>
-      <c r="J6" s="1">
-        <f t="shared" ref="J6:J45" si="1">Y6*Z6*100</f>
-        <v>10000</v>
-      </c>
-      <c r="K6" s="1">
-        <f t="shared" ref="K6:K45" si="2">Y6*6</f>
-        <v>6</v>
-      </c>
       <c r="L6" s="1">
-        <f t="shared" ref="L6:L45" si="3">Y6*4</f>
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="M6" s="1">
-        <f t="shared" ref="M6:M45" si="4">Y6*3</f>
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="N6" s="1">
-        <f t="shared" ref="N6:N45" si="5">Y6*5</f>
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="O6" s="5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="P6" s="5">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Q6" s="1">
         <v>0</v>
@@ -1597,39 +1458,13 @@
         <v>1</v>
       </c>
       <c r="V6" s="1">
-        <f t="shared" ref="V6:V45" si="6">X6*100</f>
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="W6" s="1">
-        <f t="shared" ref="W6:W45" si="7">X6*100</f>
-        <v>1000</v>
-      </c>
-      <c r="X6" s="1">
-        <v>10</v>
-      </c>
-      <c r="Y6" s="1">
-        <v>1</v>
-      </c>
-      <c r="Z6" s="2">
-        <v>100</v>
-      </c>
-      <c r="AA6" s="2">
-        <v>1</v>
-      </c>
-      <c r="AB6" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="2">
-        <v>10</v>
-      </c>
-      <c r="AD6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:32">
+    <row r="7" customHeight="1" spans="1:23">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1640,97 +1475,61 @@
         <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="G7" s="1">
         <v>2</v>
       </c>
       <c r="H7" s="1">
-        <f t="shared" ref="H7:H45" si="8">Y7*Z7*AA7/4</f>
-        <v>55</v>
+        <v>200000</v>
       </c>
       <c r="I7" s="1">
-        <f t="shared" si="0"/>
-        <v>110</v>
-      </c>
-      <c r="J7" s="1">
-        <f t="shared" si="1"/>
-        <v>22000</v>
+        <v>200000</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>34</v>
       </c>
       <c r="K7" s="1">
-        <f t="shared" si="2"/>
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="L7" s="1">
-        <f t="shared" si="3"/>
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="M7" s="1">
-        <f t="shared" si="4"/>
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="N7" s="1">
-        <f t="shared" si="5"/>
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="O7" s="5">
+        <v>15</v>
+      </c>
+      <c r="P7" s="5">
+        <v>25</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>0</v>
+      </c>
+      <c r="R7" s="1">
+        <v>0</v>
+      </c>
+      <c r="S7" s="1">
+        <v>0</v>
+      </c>
+      <c r="T7" s="5">
         <v>2</v>
       </c>
-      <c r="P7" s="5">
-        <v>10</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>1</v>
-      </c>
-      <c r="R7" s="1">
-        <v>0</v>
-      </c>
-      <c r="S7" s="1">
-        <v>0</v>
-      </c>
-      <c r="T7" s="5">
-        <v>1</v>
-      </c>
       <c r="U7" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V7" s="1">
-        <f t="shared" si="6"/>
-        <v>1100</v>
+        <v>8000</v>
       </c>
       <c r="W7" s="1">
-        <f t="shared" si="7"/>
-        <v>1100</v>
-      </c>
-      <c r="X7" s="1">
-        <v>11</v>
-      </c>
-      <c r="Y7" s="1">
-        <v>2</v>
-      </c>
-      <c r="Z7" s="2">
-        <f t="shared" ref="Z7:Z16" si="9">Z6+10</f>
-        <v>110</v>
-      </c>
-      <c r="AA7" s="2">
-        <v>1</v>
-      </c>
-      <c r="AB7" s="2">
-        <v>1</v>
-      </c>
-      <c r="AC7" s="2">
-        <f t="shared" ref="AC7:AC10" si="10">AC6+5</f>
-        <v>15</v>
-      </c>
-      <c r="AD7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="1"/>
-      <c r="AF7" s="1">
-        <v>0</v>
+        <v>8000</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:32">
+    <row r="8" customHeight="1" spans="1:23">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1741,98 +1540,61 @@
         <v>1</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="G8" s="1">
         <v>3</v>
       </c>
-      <c r="H8" s="1">
-        <f t="shared" si="8"/>
+      <c r="H8" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K8" s="1">
+        <v>100</v>
+      </c>
+      <c r="L8" s="1">
+        <v>60</v>
+      </c>
+      <c r="M8" s="1">
+        <v>35</v>
+      </c>
+      <c r="N8" s="1">
         <v>90</v>
       </c>
-      <c r="I8" s="1">
-        <f t="shared" si="0"/>
-        <v>180</v>
-      </c>
-      <c r="J8" s="1">
-        <f t="shared" si="1"/>
-        <v>36000</v>
-      </c>
-      <c r="K8" s="1">
-        <f t="shared" si="2"/>
-        <v>18</v>
-      </c>
-      <c r="L8" s="1">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-      <c r="M8" s="1">
-        <f t="shared" si="4"/>
-        <v>9</v>
-      </c>
-      <c r="N8" s="1">
-        <f t="shared" si="5"/>
-        <v>15</v>
-      </c>
       <c r="O8" s="5">
+        <v>20</v>
+      </c>
+      <c r="P8" s="2">
+        <v>30</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>0</v>
+      </c>
+      <c r="R8" s="1">
+        <v>0</v>
+      </c>
+      <c r="S8" s="1">
+        <v>0</v>
+      </c>
+      <c r="T8" s="5">
         <v>3</v>
       </c>
-      <c r="P8" s="2">
-        <f t="shared" ref="P8:P27" si="11">P7+2</f>
-        <v>12</v>
-      </c>
-      <c r="Q8" s="1">
-        <v>2</v>
-      </c>
-      <c r="R8" s="1">
-        <v>0</v>
-      </c>
-      <c r="S8" s="1">
-        <v>0</v>
-      </c>
-      <c r="T8" s="5">
-        <v>1</v>
-      </c>
       <c r="U8" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V8" s="1">
-        <f t="shared" si="6"/>
-        <v>1200</v>
+        <v>10000</v>
       </c>
       <c r="W8" s="1">
-        <f t="shared" si="7"/>
-        <v>1200</v>
-      </c>
-      <c r="X8" s="1">
-        <v>12</v>
-      </c>
-      <c r="Y8" s="1">
-        <v>3</v>
-      </c>
-      <c r="Z8" s="2">
-        <f t="shared" si="9"/>
-        <v>120</v>
-      </c>
-      <c r="AA8" s="2">
-        <v>1</v>
-      </c>
-      <c r="AB8" s="2">
-        <v>2</v>
-      </c>
-      <c r="AC8" s="2">
-        <f t="shared" si="10"/>
-        <v>20</v>
-      </c>
-      <c r="AD8" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="1"/>
-      <c r="AF8" s="1">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:32">
+    <row r="9" customHeight="1" spans="1:23">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1843,98 +1605,61 @@
         <v>1</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G9" s="1">
         <v>4</v>
       </c>
-      <c r="H9" s="1">
-        <f t="shared" si="8"/>
-        <v>130</v>
-      </c>
-      <c r="I9" s="1">
-        <f t="shared" si="0"/>
-        <v>260</v>
-      </c>
-      <c r="J9" s="1">
-        <f t="shared" si="1"/>
-        <v>52000</v>
+      <c r="H9" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="K9" s="1">
-        <f t="shared" si="2"/>
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="L9" s="1">
-        <f t="shared" si="3"/>
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="M9" s="1">
-        <f t="shared" si="4"/>
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="N9" s="1">
-        <f t="shared" si="5"/>
+        <v>90</v>
+      </c>
+      <c r="O9" s="5">
         <v>20</v>
       </c>
-      <c r="O9" s="5">
+      <c r="P9" s="2">
+        <v>30</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>0</v>
+      </c>
+      <c r="R9" s="1">
+        <v>0</v>
+      </c>
+      <c r="S9" s="1">
+        <v>0</v>
+      </c>
+      <c r="T9" s="5">
         <v>4</v>
       </c>
-      <c r="P9" s="2">
-        <f t="shared" si="11"/>
-        <v>14</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>3</v>
-      </c>
-      <c r="R9" s="1">
-        <v>0</v>
-      </c>
-      <c r="S9" s="1">
-        <v>0</v>
-      </c>
-      <c r="T9" s="5">
-        <v>1</v>
-      </c>
       <c r="U9" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V9" s="1">
-        <f t="shared" si="6"/>
-        <v>1300</v>
+        <v>15000</v>
       </c>
       <c r="W9" s="1">
-        <f t="shared" si="7"/>
-        <v>1300</v>
-      </c>
-      <c r="X9" s="1">
-        <v>13</v>
-      </c>
-      <c r="Y9" s="1">
-        <v>4</v>
-      </c>
-      <c r="Z9" s="2">
-        <f t="shared" si="9"/>
-        <v>130</v>
-      </c>
-      <c r="AA9" s="2">
-        <v>1</v>
-      </c>
-      <c r="AB9" s="2">
-        <v>3</v>
-      </c>
-      <c r="AC9" s="2">
-        <f t="shared" si="10"/>
-        <v>25</v>
-      </c>
-      <c r="AD9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="1"/>
-      <c r="AF9" s="1">
-        <v>0</v>
+        <v>15000</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:32">
+    <row r="10" customHeight="1" spans="1:23">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1945,98 +1670,61 @@
         <v>1</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="G10" s="1">
         <v>5</v>
       </c>
-      <c r="H10" s="1">
-        <f t="shared" si="8"/>
-        <v>175</v>
-      </c>
-      <c r="I10" s="1">
-        <f t="shared" si="0"/>
-        <v>350</v>
-      </c>
-      <c r="J10" s="1">
-        <f t="shared" si="1"/>
-        <v>70000</v>
+      <c r="H10" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="K10" s="1">
-        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="L10" s="1">
+        <v>60</v>
+      </c>
+      <c r="M10" s="1">
+        <v>35</v>
+      </c>
+      <c r="N10" s="1">
+        <v>90</v>
+      </c>
+      <c r="O10" s="5">
+        <v>20</v>
+      </c>
+      <c r="P10" s="2">
         <v>30</v>
       </c>
-      <c r="L10" s="1">
-        <f t="shared" si="3"/>
-        <v>20</v>
-      </c>
-      <c r="M10" s="1">
-        <f t="shared" si="4"/>
-        <v>15</v>
-      </c>
-      <c r="N10" s="1">
-        <f t="shared" si="5"/>
-        <v>25</v>
-      </c>
-      <c r="O10" s="5">
+      <c r="Q10" s="1">
+        <v>0</v>
+      </c>
+      <c r="R10" s="1">
+        <v>0</v>
+      </c>
+      <c r="S10" s="1">
+        <v>0</v>
+      </c>
+      <c r="T10" s="5">
         <v>5</v>
       </c>
-      <c r="P10" s="2">
-        <f t="shared" si="11"/>
-        <v>16</v>
-      </c>
-      <c r="Q10" s="1">
-        <v>4</v>
-      </c>
-      <c r="R10" s="1">
-        <v>0</v>
-      </c>
-      <c r="S10" s="1">
-        <v>0</v>
-      </c>
-      <c r="T10" s="5">
-        <v>1</v>
-      </c>
       <c r="U10" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="V10" s="1">
-        <f t="shared" si="6"/>
-        <v>1400</v>
+        <v>20000</v>
       </c>
       <c r="W10" s="1">
-        <f t="shared" si="7"/>
-        <v>1400</v>
-      </c>
-      <c r="X10" s="1">
-        <v>14</v>
-      </c>
-      <c r="Y10" s="1">
-        <v>5</v>
-      </c>
-      <c r="Z10" s="2">
-        <f t="shared" si="9"/>
-        <v>140</v>
-      </c>
-      <c r="AA10" s="2">
-        <v>1</v>
-      </c>
-      <c r="AB10" s="2">
-        <v>4</v>
-      </c>
-      <c r="AC10" s="2">
-        <f t="shared" si="10"/>
-        <v>30</v>
-      </c>
-      <c r="AD10" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="1"/>
-      <c r="AF10" s="1">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:32">
+    <row r="11" customHeight="1" spans="1:23">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -2047,98 +1735,61 @@
         <v>1</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G11" s="1">
         <v>6</v>
       </c>
-      <c r="H11" s="1">
-        <f t="shared" si="8"/>
-        <v>450</v>
-      </c>
-      <c r="I11" s="1">
-        <f t="shared" si="0"/>
-        <v>450</v>
-      </c>
-      <c r="J11" s="1">
-        <f t="shared" si="1"/>
-        <v>90000</v>
+      <c r="H11" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="K11" s="1">
-        <f t="shared" si="2"/>
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="L11" s="1">
-        <f t="shared" si="3"/>
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="M11" s="1">
-        <f t="shared" si="4"/>
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="N11" s="1">
-        <f t="shared" si="5"/>
+        <v>90</v>
+      </c>
+      <c r="O11" s="5">
+        <v>20</v>
+      </c>
+      <c r="P11" s="2">
         <v>30</v>
       </c>
-      <c r="O11" s="5">
+      <c r="Q11" s="1">
+        <v>0</v>
+      </c>
+      <c r="R11" s="1">
+        <v>0</v>
+      </c>
+      <c r="S11" s="1">
+        <v>0</v>
+      </c>
+      <c r="T11" s="5">
         <v>6</v>
       </c>
-      <c r="P11" s="2">
-        <f t="shared" si="11"/>
-        <v>18</v>
-      </c>
-      <c r="Q11" s="1">
-        <v>5</v>
-      </c>
-      <c r="R11" s="1">
-        <v>0</v>
-      </c>
-      <c r="S11" s="1">
-        <v>0</v>
-      </c>
-      <c r="T11" s="5">
-        <v>1</v>
-      </c>
       <c r="U11" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V11" s="1">
-        <f t="shared" si="6"/>
-        <v>1500</v>
+        <v>25000</v>
       </c>
       <c r="W11" s="1">
-        <f t="shared" si="7"/>
-        <v>1500</v>
-      </c>
-      <c r="X11" s="1">
-        <v>15</v>
-      </c>
-      <c r="Y11" s="1">
-        <v>6</v>
-      </c>
-      <c r="Z11" s="2">
-        <f t="shared" si="9"/>
-        <v>150</v>
-      </c>
-      <c r="AA11" s="2">
-        <v>2</v>
-      </c>
-      <c r="AB11" s="2">
-        <v>5</v>
-      </c>
-      <c r="AC11" s="2">
-        <f t="shared" ref="AC11:AC17" si="12">AC10+10</f>
-        <v>40</v>
-      </c>
-      <c r="AD11" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="1"/>
-      <c r="AF11" s="1">
-        <v>0</v>
+        <v>25000</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:32">
+    <row r="12" customHeight="1" spans="1:23">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -2149,98 +1800,61 @@
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="G12" s="1">
         <v>7</v>
       </c>
-      <c r="H12" s="1">
-        <f t="shared" si="8"/>
-        <v>560</v>
-      </c>
-      <c r="I12" s="1">
-        <f t="shared" si="0"/>
-        <v>560</v>
-      </c>
-      <c r="J12" s="1">
-        <f t="shared" si="1"/>
-        <v>112000</v>
+      <c r="H12" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="K12" s="1">
-        <f t="shared" si="2"/>
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="L12" s="1">
-        <f t="shared" si="3"/>
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="M12" s="1">
-        <f t="shared" si="4"/>
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="N12" s="1">
-        <f t="shared" si="5"/>
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="O12" s="5">
+        <v>20</v>
+      </c>
+      <c r="P12" s="2">
+        <v>30</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>0</v>
+      </c>
+      <c r="R12" s="1">
+        <v>0</v>
+      </c>
+      <c r="S12" s="1">
+        <v>0</v>
+      </c>
+      <c r="T12" s="5">
         <v>7</v>
       </c>
-      <c r="P12" s="2">
-        <f t="shared" si="11"/>
-        <v>20</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>6</v>
-      </c>
-      <c r="R12" s="1">
-        <v>0</v>
-      </c>
-      <c r="S12" s="1">
-        <v>0</v>
-      </c>
-      <c r="T12" s="5">
-        <v>1</v>
-      </c>
       <c r="U12" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="V12" s="1">
-        <f t="shared" si="6"/>
-        <v>1600</v>
+        <v>30000</v>
       </c>
       <c r="W12" s="1">
-        <f t="shared" si="7"/>
-        <v>1600</v>
-      </c>
-      <c r="X12" s="1">
-        <v>16</v>
-      </c>
-      <c r="Y12" s="1">
-        <v>7</v>
-      </c>
-      <c r="Z12" s="2">
-        <f t="shared" si="9"/>
-        <v>160</v>
-      </c>
-      <c r="AA12" s="2">
-        <v>2</v>
-      </c>
-      <c r="AB12" s="2">
-        <v>6</v>
-      </c>
-      <c r="AC12" s="2">
-        <f t="shared" si="12"/>
-        <v>50</v>
-      </c>
-      <c r="AD12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="1"/>
-      <c r="AF12" s="1">
-        <v>0</v>
+        <v>30000</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:32">
+    <row r="13" customHeight="1" spans="1:23">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -2251,98 +1865,61 @@
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="G13" s="1">
         <v>8</v>
       </c>
-      <c r="H13" s="1">
-        <f t="shared" si="8"/>
-        <v>680</v>
-      </c>
-      <c r="I13" s="1">
-        <f t="shared" si="0"/>
-        <v>680</v>
-      </c>
-      <c r="J13" s="1">
-        <f t="shared" si="1"/>
-        <v>136000</v>
+      <c r="H13" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="K13" s="1">
-        <f t="shared" si="2"/>
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="L13" s="1">
-        <f t="shared" si="3"/>
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="M13" s="1">
-        <f t="shared" si="4"/>
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="N13" s="1">
-        <f t="shared" si="5"/>
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="O13" s="5">
+        <v>20</v>
+      </c>
+      <c r="P13" s="2">
+        <v>30</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>0</v>
+      </c>
+      <c r="R13" s="1">
+        <v>0</v>
+      </c>
+      <c r="S13" s="1">
+        <v>0</v>
+      </c>
+      <c r="T13" s="5">
         <v>8</v>
       </c>
-      <c r="P13" s="2">
-        <f t="shared" si="11"/>
-        <v>22</v>
-      </c>
-      <c r="Q13" s="1">
-        <v>7</v>
-      </c>
-      <c r="R13" s="1">
-        <v>0</v>
-      </c>
-      <c r="S13" s="1">
-        <v>0</v>
-      </c>
-      <c r="T13" s="5">
-        <v>1</v>
-      </c>
       <c r="U13" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="V13" s="1">
-        <f t="shared" si="6"/>
-        <v>1700</v>
+        <v>40000</v>
       </c>
       <c r="W13" s="1">
-        <f t="shared" si="7"/>
-        <v>1700</v>
-      </c>
-      <c r="X13" s="1">
-        <v>17</v>
-      </c>
-      <c r="Y13" s="1">
-        <v>8</v>
-      </c>
-      <c r="Z13" s="2">
-        <f t="shared" si="9"/>
-        <v>170</v>
-      </c>
-      <c r="AA13" s="2">
-        <v>2</v>
-      </c>
-      <c r="AB13" s="2">
-        <v>7</v>
-      </c>
-      <c r="AC13" s="2">
-        <f t="shared" si="12"/>
-        <v>60</v>
-      </c>
-      <c r="AD13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE13" s="1"/>
-      <c r="AF13" s="1">
-        <v>0</v>
+        <v>40000</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:32">
+    <row r="14" customHeight="1" spans="1:23">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -2353,98 +1930,61 @@
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G14" s="1">
         <v>9</v>
       </c>
-      <c r="H14" s="1">
-        <f t="shared" si="8"/>
-        <v>810</v>
-      </c>
-      <c r="I14" s="1">
-        <f t="shared" si="0"/>
-        <v>810</v>
-      </c>
-      <c r="J14" s="1">
-        <f t="shared" si="1"/>
-        <v>162000</v>
+      <c r="H14" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="K14" s="1">
-        <f t="shared" si="2"/>
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="L14" s="1">
-        <f t="shared" si="3"/>
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="M14" s="1">
-        <f t="shared" si="4"/>
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="N14" s="1">
-        <f t="shared" si="5"/>
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="O14" s="5">
+        <v>20</v>
+      </c>
+      <c r="P14" s="2">
+        <v>30</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>0</v>
+      </c>
+      <c r="R14" s="1">
+        <v>0</v>
+      </c>
+      <c r="S14" s="1">
+        <v>0</v>
+      </c>
+      <c r="T14" s="5">
         <v>9</v>
       </c>
-      <c r="P14" s="2">
-        <f t="shared" si="11"/>
-        <v>24</v>
-      </c>
-      <c r="Q14" s="1">
-        <v>8</v>
-      </c>
-      <c r="R14" s="1">
-        <v>0</v>
-      </c>
-      <c r="S14" s="1">
-        <v>0</v>
-      </c>
-      <c r="T14" s="5">
-        <v>1</v>
-      </c>
       <c r="U14" s="5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="V14" s="1">
-        <f t="shared" si="6"/>
-        <v>1800</v>
+        <v>50000</v>
       </c>
       <c r="W14" s="1">
-        <f t="shared" si="7"/>
-        <v>1800</v>
-      </c>
-      <c r="X14" s="1">
-        <v>18</v>
-      </c>
-      <c r="Y14" s="1">
-        <v>9</v>
-      </c>
-      <c r="Z14" s="2">
-        <f t="shared" si="9"/>
-        <v>180</v>
-      </c>
-      <c r="AA14" s="2">
-        <v>2</v>
-      </c>
-      <c r="AB14" s="2">
-        <v>8</v>
-      </c>
-      <c r="AC14" s="2">
-        <f t="shared" si="12"/>
-        <v>70</v>
-      </c>
-      <c r="AD14" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="1"/>
-      <c r="AF14" s="1">
-        <v>0</v>
+        <v>50000</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:32">
+    <row r="15" customHeight="1" spans="1:23">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -2455,98 +1995,61 @@
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G15" s="1">
         <v>10</v>
       </c>
-      <c r="H15" s="1">
-        <f t="shared" si="8"/>
-        <v>950</v>
-      </c>
-      <c r="I15" s="1">
-        <f t="shared" si="0"/>
-        <v>950</v>
-      </c>
-      <c r="J15" s="1">
-        <f t="shared" si="1"/>
-        <v>190000</v>
+      <c r="H15" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="K15" s="1">
-        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="L15" s="1">
         <v>60</v>
       </c>
-      <c r="L15" s="1">
-        <f t="shared" si="3"/>
-        <v>40</v>
-      </c>
       <c r="M15" s="1">
-        <f t="shared" si="4"/>
+        <v>35</v>
+      </c>
+      <c r="N15" s="1">
+        <v>90</v>
+      </c>
+      <c r="O15" s="5">
+        <v>20</v>
+      </c>
+      <c r="P15" s="2">
         <v>30</v>
       </c>
-      <c r="N15" s="1">
-        <f t="shared" si="5"/>
-        <v>50</v>
-      </c>
-      <c r="O15" s="5">
+      <c r="Q15" s="1">
+        <v>0</v>
+      </c>
+      <c r="R15" s="1">
+        <v>0</v>
+      </c>
+      <c r="S15" s="1">
+        <v>0</v>
+      </c>
+      <c r="T15" s="5">
         <v>10</v>
       </c>
-      <c r="P15" s="2">
-        <f t="shared" si="11"/>
-        <v>26</v>
-      </c>
-      <c r="Q15" s="1">
-        <v>9</v>
-      </c>
-      <c r="R15" s="1">
-        <v>0</v>
-      </c>
-      <c r="S15" s="1">
-        <v>0</v>
-      </c>
-      <c r="T15" s="5">
-        <v>1</v>
-      </c>
       <c r="U15" s="5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="V15" s="1">
-        <f t="shared" si="6"/>
-        <v>1900</v>
+        <v>60000</v>
       </c>
       <c r="W15" s="1">
-        <f t="shared" si="7"/>
-        <v>1900</v>
-      </c>
-      <c r="X15" s="1">
-        <v>19</v>
-      </c>
-      <c r="Y15" s="1">
-        <v>10</v>
-      </c>
-      <c r="Z15" s="2">
-        <f t="shared" si="9"/>
-        <v>190</v>
-      </c>
-      <c r="AA15" s="2">
-        <v>2</v>
-      </c>
-      <c r="AB15" s="2">
-        <v>9</v>
-      </c>
-      <c r="AC15" s="2">
-        <f t="shared" si="12"/>
-        <v>80</v>
-      </c>
-      <c r="AD15" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="1"/>
-      <c r="AF15" s="1">
-        <v>0</v>
+        <v>60000</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:32">
+    <row r="16" customHeight="1" spans="1:23">
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -2557,98 +2060,61 @@
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G16" s="1">
         <v>11</v>
       </c>
-      <c r="H16" s="1">
-        <f t="shared" si="8"/>
-        <v>1650</v>
-      </c>
-      <c r="I16" s="1">
-        <f t="shared" si="0"/>
-        <v>1100</v>
-      </c>
-      <c r="J16" s="1">
-        <f t="shared" si="1"/>
-        <v>220000</v>
+      <c r="H16" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="K16" s="1">
-        <f t="shared" si="2"/>
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="L16" s="1">
-        <f t="shared" si="3"/>
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="M16" s="1">
-        <f t="shared" si="4"/>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="N16" s="1">
-        <f t="shared" si="5"/>
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="O16" s="5">
+        <v>20</v>
+      </c>
+      <c r="P16" s="2">
+        <v>30</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>0</v>
+      </c>
+      <c r="R16" s="1">
+        <v>0</v>
+      </c>
+      <c r="S16" s="1">
+        <v>0</v>
+      </c>
+      <c r="T16" s="5">
         <v>11</v>
       </c>
-      <c r="P16" s="2">
-        <f t="shared" si="11"/>
-        <v>28</v>
-      </c>
-      <c r="Q16" s="1">
-        <v>10</v>
-      </c>
-      <c r="R16" s="1">
-        <v>0</v>
-      </c>
-      <c r="S16" s="1">
-        <v>0</v>
-      </c>
-      <c r="T16" s="5">
-        <v>2</v>
-      </c>
       <c r="U16" s="5">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="V16" s="1">
-        <f t="shared" si="6"/>
-        <v>2000</v>
+        <v>70000</v>
       </c>
       <c r="W16" s="1">
-        <f t="shared" si="7"/>
-        <v>2000</v>
-      </c>
-      <c r="X16" s="1">
-        <v>20</v>
-      </c>
-      <c r="Y16" s="1">
-        <v>11</v>
-      </c>
-      <c r="Z16" s="2">
-        <f t="shared" si="9"/>
-        <v>200</v>
-      </c>
-      <c r="AA16" s="2">
-        <v>3</v>
-      </c>
-      <c r="AB16" s="2">
-        <v>10</v>
-      </c>
-      <c r="AC16" s="2">
-        <f t="shared" si="12"/>
-        <v>90</v>
-      </c>
-      <c r="AD16" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE16" s="1"/>
-      <c r="AF16" s="1">
-        <v>0</v>
+        <v>70000</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="3:32">
+    <row r="17" customHeight="1" spans="3:23">
       <c r="C17" s="1">
         <v>12</v>
       </c>
@@ -2659,98 +2125,61 @@
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="G17" s="1">
         <v>12</v>
       </c>
-      <c r="H17" s="1">
-        <f t="shared" si="8"/>
-        <v>1980</v>
-      </c>
-      <c r="I17" s="1">
-        <f t="shared" si="0"/>
-        <v>1320</v>
-      </c>
-      <c r="J17" s="1">
-        <f t="shared" si="1"/>
-        <v>264000</v>
+      <c r="H17" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="K17" s="1">
-        <f t="shared" si="2"/>
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="L17" s="1">
-        <f t="shared" si="3"/>
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="M17" s="1">
-        <f t="shared" si="4"/>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N17" s="1">
-        <f t="shared" si="5"/>
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="O17" s="5">
+        <v>20</v>
+      </c>
+      <c r="P17" s="2">
+        <v>30</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>0</v>
+      </c>
+      <c r="R17" s="1">
+        <v>0</v>
+      </c>
+      <c r="S17" s="1">
+        <v>0</v>
+      </c>
+      <c r="T17" s="5">
         <v>12</v>
       </c>
-      <c r="P17" s="2">
-        <f t="shared" si="11"/>
-        <v>30</v>
-      </c>
-      <c r="Q17" s="1">
-        <v>11</v>
-      </c>
-      <c r="R17" s="1">
-        <v>0</v>
-      </c>
-      <c r="S17" s="1">
-        <v>0</v>
-      </c>
-      <c r="T17" s="5">
-        <v>2</v>
-      </c>
       <c r="U17" s="5">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="V17" s="1">
-        <f t="shared" si="6"/>
-        <v>2100</v>
+        <v>80000</v>
       </c>
       <c r="W17" s="1">
-        <f t="shared" si="7"/>
-        <v>2100</v>
-      </c>
-      <c r="X17" s="1">
-        <v>21</v>
-      </c>
-      <c r="Y17" s="1">
-        <v>12</v>
-      </c>
-      <c r="Z17" s="2">
-        <f>Z16+20</f>
-        <v>220</v>
-      </c>
-      <c r="AA17" s="2">
-        <v>3</v>
-      </c>
-      <c r="AB17" s="2">
-        <v>11</v>
-      </c>
-      <c r="AC17" s="2">
-        <f t="shared" si="12"/>
-        <v>100</v>
-      </c>
-      <c r="AD17" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE17" s="1"/>
-      <c r="AF17" s="1">
-        <v>0</v>
+        <v>80000</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="3:32">
+    <row r="18" customHeight="1" spans="3:23">
       <c r="Q18" s="1"/>
       <c r="S18" s="1"/>
       <c r="T18" s="5"/>
@@ -2758,7 +2187,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:U5 AD3:AF5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:U5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="48">
   <si>
     <t>ID</t>
   </si>
@@ -128,10 +128,13 @@
     <t>双翼狮王</t>
   </si>
   <si>
+    <t>1E+6</t>
+  </si>
+  <si>
     <t>三头巨鳄</t>
   </si>
   <si>
-    <t>1E+8</t>
+    <t>2E+7</t>
   </si>
   <si>
     <t>腐尸君主</t>
@@ -1421,8 +1424,8 @@
       <c r="I6" s="1">
         <v>10000</v>
       </c>
-      <c r="J6" s="1">
-        <v>1000000</v>
+      <c r="J6" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="K6" s="1">
         <v>50</v>
@@ -1475,19 +1478,19 @@
         <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G7" s="1">
         <v>2</v>
       </c>
       <c r="H7" s="1">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="I7" s="1">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K7" s="1">
         <v>75</v>
@@ -1540,19 +1543,19 @@
         <v>1</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G8" s="1">
         <v>3</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K8" s="1">
         <v>100</v>
@@ -1605,19 +1608,19 @@
         <v>1</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G9" s="1">
         <v>4</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K9" s="1">
         <v>100</v>
@@ -1670,19 +1673,19 @@
         <v>1</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G10" s="1">
         <v>5</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K10" s="1">
         <v>100</v>
@@ -1735,19 +1738,19 @@
         <v>1</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G11" s="1">
         <v>6</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K11" s="1">
         <v>100</v>
@@ -1800,19 +1803,19 @@
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G12" s="1">
         <v>7</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K12" s="1">
         <v>100</v>
@@ -1865,19 +1868,19 @@
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G13" s="1">
         <v>8</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K13" s="1">
         <v>100</v>
@@ -1930,19 +1933,19 @@
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G14" s="1">
         <v>9</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K14" s="1">
         <v>100</v>
@@ -1995,19 +1998,19 @@
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G15" s="1">
         <v>10</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K15" s="1">
         <v>100</v>
@@ -2060,19 +2063,19 @@
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G16" s="1">
         <v>11</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K16" s="1">
         <v>100</v>
@@ -2125,19 +2128,19 @@
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G17" s="1">
         <v>12</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K17" s="1">
         <v>100</v>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="50">
   <si>
     <t>ID</t>
   </si>
@@ -128,28 +128,34 @@
     <t>双翼狮王</t>
   </si>
   <si>
-    <t>1E+6</t>
+    <t>6E+6</t>
   </si>
   <si>
     <t>三头巨鳄</t>
   </si>
   <si>
-    <t>2E+7</t>
+    <t>10E+7</t>
   </si>
   <si>
     <t>腐尸君主</t>
   </si>
   <si>
+    <t>10E+8</t>
+  </si>
+  <si>
+    <t>梦魇鹿神</t>
+  </si>
+  <si>
+    <t>5E+9</t>
+  </si>
+  <si>
+    <t>不朽骨龙</t>
+  </si>
+  <si>
     <t>2E+6</t>
   </si>
   <si>
     <t>1E+11</t>
-  </si>
-  <si>
-    <t>梦魇鹿神</t>
-  </si>
-  <si>
-    <t>不朽骨龙</t>
   </si>
   <si>
     <t>蛮鬃酋长</t>
@@ -1548,14 +1554,14 @@
       <c r="G8" s="1">
         <v>3</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="H8" s="1">
+        <v>500000</v>
+      </c>
+      <c r="I8" s="1">
+        <v>400000</v>
+      </c>
+      <c r="J8" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>38</v>
       </c>
       <c r="K8" s="1">
         <v>100</v>
@@ -1608,19 +1614,19 @@
         <v>1</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G9" s="1">
         <v>4</v>
       </c>
-      <c r="H9" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>37</v>
+      <c r="H9" s="1">
+        <v>2000000</v>
+      </c>
+      <c r="I9" s="1">
+        <v>2000000</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K9" s="1">
         <v>100</v>
@@ -1679,13 +1685,13 @@
         <v>5</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K10" s="1">
         <v>100</v>
@@ -1738,19 +1744,19 @@
         <v>1</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G11" s="1">
         <v>6</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K11" s="1">
         <v>100</v>
@@ -1803,19 +1809,19 @@
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G12" s="1">
         <v>7</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K12" s="1">
         <v>100</v>
@@ -1868,19 +1874,19 @@
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G13" s="1">
         <v>8</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K13" s="1">
         <v>100</v>
@@ -1933,19 +1939,19 @@
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G14" s="1">
         <v>9</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K14" s="1">
         <v>100</v>
@@ -1998,19 +2004,19 @@
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G15" s="1">
         <v>10</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K15" s="1">
         <v>100</v>
@@ -2063,19 +2069,19 @@
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G16" s="1">
         <v>11</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K16" s="1">
         <v>100</v>
@@ -2128,19 +2134,19 @@
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G17" s="1">
         <v>12</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K17" s="1">
         <v>100</v>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -1490,7 +1490,7 @@
         <v>2</v>
       </c>
       <c r="H7" s="1">
-        <v>100000</v>
+        <v>120000</v>
       </c>
       <c r="I7" s="1">
         <v>100000</v>
@@ -1555,7 +1555,7 @@
         <v>3</v>
       </c>
       <c r="H8" s="1">
-        <v>500000</v>
+        <v>800000</v>
       </c>
       <c r="I8" s="1">
         <v>400000</v>
@@ -1620,7 +1620,7 @@
         <v>4</v>
       </c>
       <c r="H9" s="1">
-        <v>2000000</v>
+        <v>2400000</v>
       </c>
       <c r="I9" s="1">
         <v>2000000</v>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -1151,14 +1151,13 @@
     <col min="7" max="7" width="9.58333333333333" style="1" customWidth="1"/>
     <col min="8" max="8" width="15.4166666666667" style="2" customWidth="1"/>
     <col min="9" max="9" width="12.1666666666667" style="2" customWidth="1"/>
-    <col min="10" max="10" width="11" style="2" customWidth="1"/>
-    <col min="11" max="11" width="13.6666666666667" style="2" customWidth="1"/>
+    <col min="10" max="11" width="11" style="2" customWidth="1"/>
     <col min="12" max="12" width="11.1666666666667" style="2" customWidth="1"/>
     <col min="13" max="13" width="10" style="2" customWidth="1"/>
     <col min="14" max="14" width="10.25" style="2" customWidth="1"/>
     <col min="15" max="15" width="8.08333333333333" style="2" customWidth="1"/>
     <col min="16" max="16" width="9.91666666666667" style="2" customWidth="1"/>
-    <col min="17" max="17" width="10.75" style="2" customWidth="1"/>
+    <col min="17" max="17" width="8.16666666666667" style="2" customWidth="1"/>
     <col min="18" max="18" width="7.5" style="2" customWidth="1"/>
     <col min="19" max="19" width="8.75" style="2" customWidth="1"/>
     <col min="20" max="20" width="7.50833333333333" style="2" customWidth="1"/>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="53">
   <si>
     <t>ID</t>
   </si>
@@ -152,13 +152,22 @@
     <t>不朽骨龙</t>
   </si>
   <si>
-    <t>2E+6</t>
-  </si>
-  <si>
-    <t>1E+11</t>
+    <t>10E+6</t>
+  </si>
+  <si>
+    <t>5E+6</t>
+  </si>
+  <si>
+    <t>2E+10</t>
   </si>
   <si>
     <t>蛮鬃酋长</t>
+  </si>
+  <si>
+    <t>2E+16</t>
+  </si>
+  <si>
+    <t>1E+21</t>
   </si>
   <si>
     <t>炎魔领主</t>
@@ -1628,22 +1637,22 @@
         <v>39</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="L9" s="1">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="M9" s="1">
+        <v>45</v>
+      </c>
+      <c r="N9" s="1">
+        <v>120</v>
+      </c>
+      <c r="O9" s="5">
+        <v>25</v>
+      </c>
+      <c r="P9" s="2">
         <v>35</v>
-      </c>
-      <c r="N9" s="1">
-        <v>90</v>
-      </c>
-      <c r="O9" s="5">
-        <v>20</v>
-      </c>
-      <c r="P9" s="2">
-        <v>30</v>
       </c>
       <c r="Q9" s="1">
         <v>0</v>
@@ -1687,28 +1696,28 @@
         <v>41</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="L10" s="1">
+        <v>90</v>
+      </c>
+      <c r="M10" s="1">
         <v>60</v>
       </c>
-      <c r="M10" s="1">
-        <v>35</v>
-      </c>
       <c r="N10" s="1">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="O10" s="5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P10" s="2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="Q10" s="1">
         <v>0</v>
@@ -1743,19 +1752,19 @@
         <v>1</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G11" s="1">
         <v>6</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K11" s="1">
         <v>100</v>
@@ -1808,19 +1817,19 @@
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G12" s="1">
         <v>7</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K12" s="1">
         <v>100</v>
@@ -1873,19 +1882,19 @@
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G13" s="1">
         <v>8</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K13" s="1">
         <v>100</v>
@@ -1938,19 +1947,19 @@
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G14" s="1">
         <v>9</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K14" s="1">
         <v>100</v>
@@ -2003,19 +2012,19 @@
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G15" s="1">
         <v>10</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K15" s="1">
         <v>100</v>
@@ -2068,19 +2077,19 @@
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G16" s="1">
         <v>11</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K16" s="1">
         <v>100</v>
@@ -2133,19 +2142,19 @@
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G17" s="1">
         <v>12</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K17" s="1">
         <v>100</v>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="53">
   <si>
     <t>ID</t>
   </si>
@@ -152,25 +152,25 @@
     <t>不朽骨龙</t>
   </si>
   <si>
-    <t>10E+6</t>
-  </si>
-  <si>
-    <t>5E+6</t>
-  </si>
-  <si>
     <t>2E+10</t>
   </si>
   <si>
     <t>蛮鬃酋长</t>
   </si>
   <si>
+    <t>2E+7</t>
+  </si>
+  <si>
+    <t>1E+11</t>
+  </si>
+  <si>
+    <t>炎魔领主</t>
+  </si>
+  <si>
     <t>2E+16</t>
   </si>
   <si>
     <t>1E+21</t>
-  </si>
-  <si>
-    <t>炎魔领主</t>
   </si>
   <si>
     <t>冰霜巨龙</t>
@@ -1692,14 +1692,14 @@
       <c r="G10" s="1">
         <v>5</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H10" s="1">
+        <v>7200000</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J10" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>43</v>
       </c>
       <c r="K10" s="1">
         <v>150</v>
@@ -1752,37 +1752,37 @@
         <v>1</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G11" s="1">
         <v>6</v>
       </c>
       <c r="H11" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="K11" s="1">
+        <v>175</v>
+      </c>
+      <c r="L11" s="1">
+        <v>105</v>
+      </c>
+      <c r="M11" s="1">
+        <v>75</v>
+      </c>
+      <c r="N11" s="1">
+        <v>180</v>
+      </c>
+      <c r="O11" s="5">
+        <v>35</v>
+      </c>
+      <c r="P11" s="2">
         <v>45</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="K11" s="1">
-        <v>100</v>
-      </c>
-      <c r="L11" s="1">
-        <v>60</v>
-      </c>
-      <c r="M11" s="1">
-        <v>35</v>
-      </c>
-      <c r="N11" s="1">
-        <v>90</v>
-      </c>
-      <c r="O11" s="5">
-        <v>20</v>
-      </c>
-      <c r="P11" s="2">
-        <v>30</v>
       </c>
       <c r="Q11" s="1">
         <v>0</v>
@@ -1817,22 +1817,22 @@
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G12" s="1">
         <v>7</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="L12" s="1">
         <v>60</v>
@@ -1888,16 +1888,16 @@
         <v>8</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="L13" s="1">
         <v>60</v>
@@ -1953,16 +1953,16 @@
         <v>9</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="L14" s="1">
         <v>60</v>
@@ -2018,16 +2018,16 @@
         <v>10</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="L15" s="1">
         <v>60</v>
@@ -2083,16 +2083,16 @@
         <v>11</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="L16" s="1">
         <v>60</v>
@@ -2148,16 +2148,16 @@
         <v>12</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="L17" s="1">
         <v>60</v>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -26,8 +26,43 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="X3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+boss刷新出来的概率</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="61">
+  <si>
+    <t>#</t>
+  </si>
   <si>
     <t>ID</t>
   </si>
@@ -92,6 +127,9 @@
     <t>掉落金币</t>
   </si>
   <si>
+    <t>Rate</t>
+  </si>
+  <si>
     <t>Id</t>
   </si>
   <si>
@@ -125,34 +163,52 @@
     <t>long</t>
   </si>
   <si>
+    <t>刷新时间</t>
+  </si>
+  <si>
     <t>双翼狮王</t>
   </si>
   <si>
     <t>6E+6</t>
   </si>
   <si>
+    <t>15分钟</t>
+  </si>
+  <si>
     <t>三头巨鳄</t>
   </si>
   <si>
     <t>10E+7</t>
   </si>
   <si>
+    <t>半小时</t>
+  </si>
+  <si>
     <t>腐尸君主</t>
   </si>
   <si>
     <t>10E+8</t>
   </si>
   <si>
+    <t>1小时</t>
+  </si>
+  <si>
     <t>梦魇鹿神</t>
   </si>
   <si>
     <t>5E+9</t>
   </si>
   <si>
+    <t>1.5小时</t>
+  </si>
+  <si>
     <t>不朽骨龙</t>
   </si>
   <si>
     <t>2E+10</t>
+  </si>
+  <si>
+    <t>2小时</t>
   </si>
   <si>
     <t>蛮鬃酋长</t>
@@ -199,7 +255,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -363,6 +419,17 @@
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -1148,7 +1215,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W18"/>
+  <dimension ref="A1:Y18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1173,10 +1240,12 @@
     <col min="21" max="21" width="8.33333333333333" style="2" customWidth="1"/>
     <col min="22" max="22" width="11.6666666666667" style="2" customWidth="1"/>
     <col min="23" max="23" width="11.1666666666667" style="2" customWidth="1"/>
-    <col min="24" max="16384" width="9" style="2"/>
+    <col min="24" max="24" width="14.25" style="2" customWidth="1"/>
+    <col min="25" max="25" width="11.8333333333333" style="2" customWidth="1"/>
+    <col min="26" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:23">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="H1" s="3"/>
@@ -1195,8 +1264,12 @@
       <c r="U1" s="2"/>
       <c r="V1" s="2"/>
       <c r="W1" s="2"/>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:23">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="I2" s="2"/>
@@ -1214,209 +1287,225 @@
       <c r="U2" s="2"/>
       <c r="V2" s="2"/>
       <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
+      <c r="Y2" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:23">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="4" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S3" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U3" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V3" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="W3" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="X3" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:23">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="T4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="U4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="V4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="W4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="X4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="S4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="T4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="U4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="V4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="W4" s="4" t="s">
-        <v>28</v>
-      </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:23">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="V5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="W5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="X5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="W5" s="4" t="s">
-        <v>31</v>
+      <c r="Y5" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:23">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1427,7 +1516,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -1439,7 +1528,7 @@
         <v>10000</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K6" s="1">
         <v>50</v>
@@ -1480,8 +1569,14 @@
       <c r="W6" s="1">
         <v>5000</v>
       </c>
+      <c r="X6" s="1">
+        <v>4500</v>
+      </c>
+      <c r="Y6" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="7" customHeight="1" spans="1:23">
+    <row r="7" customHeight="1" spans="1:25">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1492,7 +1587,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G7" s="1">
         <v>2</v>
@@ -1504,7 +1599,7 @@
         <v>100000</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K7" s="1">
         <v>75</v>
@@ -1545,8 +1640,14 @@
       <c r="W7" s="1">
         <v>8000</v>
       </c>
+      <c r="X7" s="1">
+        <v>9000</v>
+      </c>
+      <c r="Y7" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="8" customHeight="1" spans="1:23">
+    <row r="8" customHeight="1" spans="1:25">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1557,7 +1658,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G8" s="1">
         <v>3</v>
@@ -1569,7 +1670,7 @@
         <v>400000</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="K8" s="1">
         <v>100</v>
@@ -1610,8 +1711,14 @@
       <c r="W8" s="1">
         <v>10000</v>
       </c>
+      <c r="X8" s="1">
+        <v>18000</v>
+      </c>
+      <c r="Y8" s="2" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="9" customHeight="1" spans="1:23">
+    <row r="9" customHeight="1" spans="1:25">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1622,7 +1729,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G9" s="1">
         <v>4</v>
@@ -1634,7 +1741,7 @@
         <v>2000000</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="K9" s="1">
         <v>125</v>
@@ -1675,8 +1782,14 @@
       <c r="W9" s="1">
         <v>15000</v>
       </c>
+      <c r="X9" s="1">
+        <v>27000</v>
+      </c>
+      <c r="Y9" s="2" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="10" customHeight="1" spans="1:23">
+    <row r="10" customHeight="1" spans="1:25">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1687,7 +1800,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G10" s="1">
         <v>5</v>
@@ -1696,10 +1809,10 @@
         <v>7200000</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="K10" s="1">
         <v>150</v>
@@ -1740,8 +1853,14 @@
       <c r="W10" s="1">
         <v>20000</v>
       </c>
+      <c r="X10" s="1">
+        <v>36000</v>
+      </c>
+      <c r="Y10" s="2" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="11" customHeight="1" spans="1:23">
+    <row r="11" customHeight="1" spans="1:25">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1752,19 +1871,19 @@
         <v>1</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G11" s="1">
         <v>6</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="K11" s="1">
         <v>175</v>
@@ -1805,8 +1924,14 @@
       <c r="W11" s="1">
         <v>25000</v>
       </c>
+      <c r="X11" s="1">
+        <v>36000</v>
+      </c>
+      <c r="Y11" s="2" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="12" customHeight="1" spans="1:23">
+    <row r="12" customHeight="1" spans="1:25">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1817,19 +1942,19 @@
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G12" s="1">
         <v>7</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="K12" s="1">
         <v>150</v>
@@ -1870,8 +1995,14 @@
       <c r="W12" s="1">
         <v>30000</v>
       </c>
+      <c r="X12" s="1">
+        <v>36000</v>
+      </c>
+      <c r="Y12" s="2" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="13" customHeight="1" spans="1:23">
+    <row r="13" customHeight="1" spans="1:25">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1882,19 +2013,19 @@
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G13" s="1">
         <v>8</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="K13" s="1">
         <v>150</v>
@@ -1935,8 +2066,14 @@
       <c r="W13" s="1">
         <v>40000</v>
       </c>
+      <c r="X13" s="1">
+        <v>36000</v>
+      </c>
+      <c r="Y13" s="2" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="14" customHeight="1" spans="1:23">
+    <row r="14" customHeight="1" spans="1:25">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -1947,19 +2084,19 @@
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G14" s="1">
         <v>9</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="K14" s="1">
         <v>150</v>
@@ -2000,8 +2137,14 @@
       <c r="W14" s="1">
         <v>50000</v>
       </c>
+      <c r="X14" s="1">
+        <v>36000</v>
+      </c>
+      <c r="Y14" s="2" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="15" customHeight="1" spans="1:23">
+    <row r="15" customHeight="1" spans="1:25">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -2012,19 +2155,19 @@
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="G15" s="1">
         <v>10</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="K15" s="1">
         <v>150</v>
@@ -2065,8 +2208,14 @@
       <c r="W15" s="1">
         <v>60000</v>
       </c>
+      <c r="X15" s="1">
+        <v>36000</v>
+      </c>
+      <c r="Y15" s="2" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="16" customHeight="1" spans="1:23">
+    <row r="16" customHeight="1" spans="1:25">
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -2077,19 +2226,19 @@
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G16" s="1">
         <v>11</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="K16" s="1">
         <v>150</v>
@@ -2130,8 +2279,14 @@
       <c r="W16" s="1">
         <v>70000</v>
       </c>
+      <c r="X16" s="1">
+        <v>36000</v>
+      </c>
+      <c r="Y16" s="2" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="17" customHeight="1" spans="3:23">
+    <row r="17" customHeight="1" spans="3:25">
       <c r="C17" s="1">
         <v>12</v>
       </c>
@@ -2142,19 +2297,19 @@
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G17" s="1">
         <v>12</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="K17" s="1">
         <v>150</v>
@@ -2195,8 +2350,14 @@
       <c r="W17" s="1">
         <v>80000</v>
       </c>
+      <c r="X17" s="1">
+        <v>36000</v>
+      </c>
+      <c r="Y17" s="2" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="18" customHeight="1" spans="3:23">
+    <row r="18" customHeight="1" spans="3:25">
       <c r="Q18" s="1"/>
       <c r="S18" s="1"/>
       <c r="T18" s="5"/>
@@ -2210,5 +2371,6 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="61">
   <si>
     <t>#</t>
   </si>
@@ -214,7 +214,7 @@
     <t>蛮鬃酋长</t>
   </si>
   <si>
-    <t>2E+7</t>
+    <t>3E+7</t>
   </si>
   <si>
     <t>1E+11</t>
@@ -421,12 +421,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1215,7 +1215,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Y18"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1876,8 +1876,8 @@
       <c r="G11" s="1">
         <v>6</v>
       </c>
-      <c r="H11" s="6" t="s">
-        <v>51</v>
+      <c r="H11" s="1">
+        <v>36000000</v>
       </c>
       <c r="I11" s="6" t="s">
         <v>51</v>
@@ -2362,6 +2362,9 @@
       <c r="S18" s="1"/>
       <c r="T18" s="5"/>
       <c r="U18" s="5"/>
+    </row>
+    <row r="24" customHeight="1" spans="3:25">
+      <c r="J24" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -32,7 +32,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="X3" authorId="0">
+    <comment ref="Y3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="74">
   <si>
     <t>#</t>
   </si>
@@ -115,6 +115,9 @@
     <t>MoveSpeed</t>
   </si>
   <si>
+    <t>Cd</t>
+  </si>
+  <si>
     <t>Lucky</t>
   </si>
   <si>
@@ -130,6 +133,12 @@
     <t>Rate</t>
   </si>
   <si>
+    <t>SkillIdList</t>
+  </si>
+  <si>
+    <t>RuneCount</t>
+  </si>
+  <si>
     <t>Id</t>
   </si>
   <si>
@@ -163,6 +172,9 @@
     <t>long</t>
   </si>
   <si>
+    <t>int[]</t>
+  </si>
+  <si>
     <t>刷新时间</t>
   </si>
   <si>
@@ -199,6 +211,9 @@
     <t>5E+9</t>
   </si>
   <si>
+    <t>3002</t>
+  </si>
+  <si>
     <t>1.5小时</t>
   </si>
   <si>
@@ -208,6 +223,9 @@
     <t>2E+10</t>
   </si>
   <si>
+    <t>2002</t>
+  </si>
+  <si>
     <t>2小时</t>
   </si>
   <si>
@@ -220,6 +238,9 @@
     <t>1E+11</t>
   </si>
   <si>
+    <t>1002</t>
+  </si>
+  <si>
     <t>炎魔领主</t>
   </si>
   <si>
@@ -229,19 +250,37 @@
     <t>1E+21</t>
   </si>
   <si>
+    <t>3002,3003</t>
+  </si>
+  <si>
     <t>冰霜巨龙</t>
   </si>
   <si>
+    <t>2002,2003</t>
+  </si>
+  <si>
     <t>痛苦女王</t>
   </si>
   <si>
+    <t>1002,1003</t>
+  </si>
+  <si>
     <t>野蛮酋长</t>
   </si>
   <si>
+    <t>3002,3003,3004</t>
+  </si>
+  <si>
     <t>终末主宰</t>
   </si>
   <si>
+    <t>2002,2003,2004</t>
+  </si>
+  <si>
     <t>毁灭之王</t>
+  </si>
+  <si>
+    <t>1002,1003,1004</t>
   </si>
 </sst>
 </file>
@@ -896,6 +935,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1215,7 +1255,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Y24"/>
+  <dimension ref="A1:AB24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1235,17 +1275,17 @@
     <col min="16" max="16" width="9.91666666666667" style="2" customWidth="1"/>
     <col min="17" max="17" width="8.16666666666667" style="2" customWidth="1"/>
     <col min="18" max="18" width="7.5" style="2" customWidth="1"/>
-    <col min="19" max="19" width="8.75" style="2" customWidth="1"/>
-    <col min="20" max="20" width="7.50833333333333" style="2" customWidth="1"/>
-    <col min="21" max="21" width="8.33333333333333" style="2" customWidth="1"/>
-    <col min="22" max="22" width="11.6666666666667" style="2" customWidth="1"/>
-    <col min="23" max="23" width="11.1666666666667" style="2" customWidth="1"/>
-    <col min="24" max="24" width="14.25" style="2" customWidth="1"/>
-    <col min="25" max="25" width="11.8333333333333" style="2" customWidth="1"/>
-    <col min="26" max="16384" width="9" style="2"/>
+    <col min="19" max="20" width="8.75" style="2" customWidth="1"/>
+    <col min="21" max="21" width="7.50833333333333" style="2" customWidth="1"/>
+    <col min="22" max="22" width="8.33333333333333" style="2" customWidth="1"/>
+    <col min="23" max="23" width="11.6666666666667" style="2" customWidth="1"/>
+    <col min="24" max="24" width="11.1666666666667" style="2" customWidth="1"/>
+    <col min="25" max="27" width="14.25" style="2" customWidth="1"/>
+    <col min="28" max="28" width="11.8333333333333" style="2" customWidth="1"/>
+    <col min="29" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:25">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="H1" s="3"/>
@@ -1265,11 +1305,14 @@
       <c r="V1" s="2"/>
       <c r="W1" s="2"/>
       <c r="X1" s="2"/>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="2"/>
+      <c r="Z1" s="2"/>
+      <c r="AA1" s="2"/>
+      <c r="AB1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:25">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="I2" s="2"/>
@@ -1288,11 +1331,14 @@
       <c r="V2" s="2"/>
       <c r="W2" s="2"/>
       <c r="X2" s="2"/>
-      <c r="Y2" s="1" t="s">
+      <c r="Y2" s="2"/>
+      <c r="Z2" s="2"/>
+      <c r="AA2" s="2"/>
+      <c r="AB2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:25">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="4" t="s">
@@ -1361,33 +1407,42 @@
       <c r="X3" s="4" t="s">
         <v>22</v>
       </c>
+      <c r="Y3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA3" s="4" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:25">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>3</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>5</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>9</v>
@@ -1423,89 +1478,107 @@
         <v>19</v>
       </c>
       <c r="V4" s="4" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="W4" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="X4" s="4" t="s">
-        <v>22</v>
+        <v>33</v>
+      </c>
+      <c r="Y4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA4" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:25">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="Y5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y5" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="Z5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB5" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:25">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1516,7 +1589,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -1528,7 +1601,7 @@
         <v>10000</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K6" s="1">
         <v>50</v>
@@ -1557,26 +1630,29 @@
       <c r="S6" s="1">
         <v>0</v>
       </c>
-      <c r="T6" s="5">
-        <v>1</v>
+      <c r="T6" s="1">
+        <v>0</v>
       </c>
       <c r="U6" s="5">
         <v>1</v>
       </c>
-      <c r="V6" s="1">
-        <v>5000</v>
+      <c r="V6" s="5">
+        <v>1</v>
       </c>
       <c r="W6" s="1">
         <v>5000</v>
       </c>
       <c r="X6" s="1">
+        <v>5000</v>
+      </c>
+      <c r="Y6" s="1">
         <v>4500</v>
       </c>
-      <c r="Y6" s="1" t="s">
-        <v>37</v>
+      <c r="AB6" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:25">
+    <row r="7" customHeight="1" spans="1:28">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1587,7 +1663,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G7" s="1">
         <v>2</v>
@@ -1599,7 +1675,7 @@
         <v>100000</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="K7" s="1">
         <v>75</v>
@@ -1628,26 +1704,31 @@
       <c r="S7" s="1">
         <v>0</v>
       </c>
-      <c r="T7" s="5">
-        <v>2</v>
+      <c r="T7" s="1">
+        <v>0</v>
       </c>
       <c r="U7" s="5">
         <v>2</v>
       </c>
-      <c r="V7" s="1">
-        <v>8000</v>
+      <c r="V7" s="5">
+        <v>2</v>
       </c>
       <c r="W7" s="1">
         <v>8000</v>
       </c>
       <c r="X7" s="1">
+        <v>8000</v>
+      </c>
+      <c r="Y7" s="1">
         <v>9000</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>40</v>
+      <c r="Z7" s="1"/>
+      <c r="AA7" s="1"/>
+      <c r="AB7" s="2" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:25">
+    <row r="8" customHeight="1" spans="1:28">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1658,7 +1739,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G8" s="1">
         <v>3</v>
@@ -1670,7 +1751,7 @@
         <v>400000</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K8" s="1">
         <v>100</v>
@@ -1699,26 +1780,31 @@
       <c r="S8" s="1">
         <v>0</v>
       </c>
-      <c r="T8" s="5">
-        <v>3</v>
+      <c r="T8" s="1">
+        <v>0</v>
       </c>
       <c r="U8" s="5">
         <v>3</v>
       </c>
-      <c r="V8" s="1">
-        <v>10000</v>
+      <c r="V8" s="5">
+        <v>3</v>
       </c>
       <c r="W8" s="1">
         <v>10000</v>
       </c>
       <c r="X8" s="1">
+        <v>10000</v>
+      </c>
+      <c r="Y8" s="1">
         <v>18000</v>
       </c>
-      <c r="Y8" s="2" t="s">
-        <v>43</v>
+      <c r="Z8" s="1"/>
+      <c r="AA8" s="1"/>
+      <c r="AB8" s="2" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:25">
+    <row r="9" customHeight="1" spans="1:28">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1729,7 +1815,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G9" s="1">
         <v>4</v>
@@ -1741,7 +1827,7 @@
         <v>2000000</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K9" s="1">
         <v>125</v>
@@ -1770,26 +1856,33 @@
       <c r="S9" s="1">
         <v>0</v>
       </c>
-      <c r="T9" s="5">
-        <v>4</v>
+      <c r="T9" s="1">
+        <v>0</v>
       </c>
       <c r="U9" s="5">
         <v>4</v>
       </c>
-      <c r="V9" s="1">
-        <v>15000</v>
+      <c r="V9" s="5">
+        <v>4</v>
       </c>
       <c r="W9" s="1">
         <v>15000</v>
       </c>
       <c r="X9" s="1">
+        <v>15000</v>
+      </c>
+      <c r="Y9" s="1">
         <v>27000</v>
       </c>
-      <c r="Y9" s="2" t="s">
-        <v>46</v>
+      <c r="Z9" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA9" s="1"/>
+      <c r="AB9" s="2" t="s">
+        <v>51</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:25">
+    <row r="10" customHeight="1" spans="1:28">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1800,7 +1893,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G10" s="1">
         <v>5</v>
@@ -1809,10 +1902,10 @@
         <v>7200000</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K10" s="1">
         <v>150</v>
@@ -1841,26 +1934,33 @@
       <c r="S10" s="1">
         <v>0</v>
       </c>
-      <c r="T10" s="5">
-        <v>5</v>
+      <c r="T10" s="1">
+        <v>0</v>
       </c>
       <c r="U10" s="5">
         <v>5</v>
       </c>
-      <c r="V10" s="1">
-        <v>20000</v>
+      <c r="V10" s="5">
+        <v>5</v>
       </c>
       <c r="W10" s="1">
         <v>20000</v>
       </c>
       <c r="X10" s="1">
+        <v>20000</v>
+      </c>
+      <c r="Y10" s="1">
         <v>36000</v>
       </c>
-      <c r="Y10" s="2" t="s">
-        <v>49</v>
+      <c r="Z10" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA10" s="1"/>
+      <c r="AB10" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:25">
+    <row r="11" customHeight="1" spans="1:28">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1871,19 +1971,19 @@
         <v>1</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="G11" s="1">
         <v>6</v>
       </c>
       <c r="H11" s="1">
-        <v>36000000</v>
+        <v>20000000</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="K11" s="1">
         <v>175</v>
@@ -1912,26 +2012,33 @@
       <c r="S11" s="1">
         <v>0</v>
       </c>
-      <c r="T11" s="5">
-        <v>6</v>
+      <c r="T11" s="1">
+        <v>0</v>
       </c>
       <c r="U11" s="5">
         <v>6</v>
       </c>
-      <c r="V11" s="1">
-        <v>25000</v>
+      <c r="V11" s="5">
+        <v>6</v>
       </c>
       <c r="W11" s="1">
         <v>25000</v>
       </c>
       <c r="X11" s="1">
+        <v>25000</v>
+      </c>
+      <c r="Y11" s="1">
         <v>36000</v>
       </c>
-      <c r="Y11" s="2" t="s">
-        <v>49</v>
+      <c r="Z11" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA11" s="1"/>
+      <c r="AB11" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:25">
+    <row r="12" customHeight="1" spans="1:28">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1942,19 +2049,19 @@
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G12" s="1">
         <v>7</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="K12" s="1">
         <v>150</v>
@@ -1983,26 +2090,33 @@
       <c r="S12" s="1">
         <v>0</v>
       </c>
-      <c r="T12" s="5">
-        <v>7</v>
+      <c r="T12" s="1">
+        <v>0</v>
       </c>
       <c r="U12" s="5">
         <v>7</v>
       </c>
-      <c r="V12" s="1">
-        <v>30000</v>
+      <c r="V12" s="5">
+        <v>7</v>
       </c>
       <c r="W12" s="1">
         <v>30000</v>
       </c>
       <c r="X12" s="1">
+        <v>30000</v>
+      </c>
+      <c r="Y12" s="1">
         <v>36000</v>
       </c>
-      <c r="Y12" s="2" t="s">
-        <v>49</v>
+      <c r="Z12" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA12" s="1"/>
+      <c r="AB12" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:25">
+    <row r="13" customHeight="1" spans="1:28">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -2013,19 +2127,19 @@
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="G13" s="1">
         <v>8</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="K13" s="1">
         <v>150</v>
@@ -2054,26 +2168,33 @@
       <c r="S13" s="1">
         <v>0</v>
       </c>
-      <c r="T13" s="5">
-        <v>8</v>
+      <c r="T13" s="1">
+        <v>0</v>
       </c>
       <c r="U13" s="5">
         <v>8</v>
       </c>
-      <c r="V13" s="1">
-        <v>40000</v>
+      <c r="V13" s="5">
+        <v>8</v>
       </c>
       <c r="W13" s="1">
         <v>40000</v>
       </c>
       <c r="X13" s="1">
+        <v>40000</v>
+      </c>
+      <c r="Y13" s="1">
         <v>36000</v>
       </c>
-      <c r="Y13" s="2" t="s">
-        <v>49</v>
+      <c r="Z13" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA13" s="1"/>
+      <c r="AB13" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:25">
+    <row r="14" customHeight="1" spans="1:28">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -2084,19 +2205,19 @@
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="G14" s="1">
         <v>9</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="K14" s="1">
         <v>150</v>
@@ -2125,26 +2246,33 @@
       <c r="S14" s="1">
         <v>0</v>
       </c>
-      <c r="T14" s="5">
-        <v>9</v>
+      <c r="T14" s="1">
+        <v>0</v>
       </c>
       <c r="U14" s="5">
         <v>9</v>
       </c>
-      <c r="V14" s="1">
-        <v>50000</v>
+      <c r="V14" s="5">
+        <v>9</v>
       </c>
       <c r="W14" s="1">
         <v>50000</v>
       </c>
       <c r="X14" s="1">
+        <v>50000</v>
+      </c>
+      <c r="Y14" s="1">
         <v>36000</v>
       </c>
-      <c r="Y14" s="2" t="s">
-        <v>49</v>
+      <c r="Z14" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA14" s="1"/>
+      <c r="AB14" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:25">
+    <row r="15" customHeight="1" spans="1:28">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -2155,19 +2283,19 @@
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G15" s="1">
         <v>10</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="K15" s="1">
         <v>150</v>
@@ -2196,26 +2324,33 @@
       <c r="S15" s="1">
         <v>0</v>
       </c>
-      <c r="T15" s="5">
-        <v>10</v>
+      <c r="T15" s="1">
+        <v>0</v>
       </c>
       <c r="U15" s="5">
         <v>10</v>
       </c>
-      <c r="V15" s="1">
-        <v>60000</v>
+      <c r="V15" s="5">
+        <v>10</v>
       </c>
       <c r="W15" s="1">
         <v>60000</v>
       </c>
       <c r="X15" s="1">
+        <v>60000</v>
+      </c>
+      <c r="Y15" s="1">
         <v>36000</v>
       </c>
-      <c r="Y15" s="2" t="s">
-        <v>49</v>
+      <c r="Z15" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA15" s="1"/>
+      <c r="AB15" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:25">
+    <row r="16" customHeight="1" spans="1:28">
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -2226,19 +2361,19 @@
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="G16" s="1">
         <v>11</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="K16" s="1">
         <v>150</v>
@@ -2267,26 +2402,33 @@
       <c r="S16" s="1">
         <v>0</v>
       </c>
-      <c r="T16" s="5">
-        <v>11</v>
+      <c r="T16" s="1">
+        <v>0</v>
       </c>
       <c r="U16" s="5">
         <v>11</v>
       </c>
-      <c r="V16" s="1">
-        <v>70000</v>
+      <c r="V16" s="5">
+        <v>11</v>
       </c>
       <c r="W16" s="1">
         <v>70000</v>
       </c>
       <c r="X16" s="1">
+        <v>70000</v>
+      </c>
+      <c r="Y16" s="1">
         <v>36000</v>
       </c>
-      <c r="Y16" s="2" t="s">
-        <v>49</v>
+      <c r="Z16" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="AA16" s="1"/>
+      <c r="AB16" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="3:25">
+    <row r="17" customHeight="1" spans="3:28">
       <c r="C17" s="1">
         <v>12</v>
       </c>
@@ -2297,19 +2439,19 @@
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="G17" s="1">
         <v>12</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="K17" s="1">
         <v>150</v>
@@ -2338,37 +2480,45 @@
       <c r="S17" s="1">
         <v>0</v>
       </c>
-      <c r="T17" s="5">
-        <v>12</v>
+      <c r="T17" s="1">
+        <v>0</v>
       </c>
       <c r="U17" s="5">
         <v>12</v>
       </c>
-      <c r="V17" s="1">
-        <v>80000</v>
+      <c r="V17" s="5">
+        <v>12</v>
       </c>
       <c r="W17" s="1">
         <v>80000</v>
       </c>
       <c r="X17" s="1">
+        <v>80000</v>
+      </c>
+      <c r="Y17" s="1">
         <v>36000</v>
       </c>
-      <c r="Y17" s="2" t="s">
-        <v>49</v>
+      <c r="Z17" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA17" s="1"/>
+      <c r="AB17" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="3:25">
+    <row r="18" customHeight="1" spans="3:28">
       <c r="Q18" s="1"/>
       <c r="S18" s="1"/>
-      <c r="T18" s="5"/>
+      <c r="T18" s="1"/>
       <c r="U18" s="5"/>
+      <c r="V18" s="5"/>
     </row>
-    <row r="24" customHeight="1" spans="3:25">
+    <row r="24" customHeight="1" spans="3:28">
       <c r="J24" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:U5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="T3 AA3 T4 AA4 T5 AA5 Z3:Z5 C3:S5 U3:V5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -460,12 +465,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1796,7 +1801,7 @@
         <v>10000</v>
       </c>
       <c r="Y8" s="1">
-        <v>18000</v>
+        <v>13500</v>
       </c>
       <c r="Z8" s="1"/>
       <c r="AA8" s="1"/>
@@ -1872,7 +1877,7 @@
         <v>15000</v>
       </c>
       <c r="Y9" s="1">
-        <v>27000</v>
+        <v>18000</v>
       </c>
       <c r="Z9" s="6" t="s">
         <v>50</v>
@@ -1950,7 +1955,7 @@
         <v>20000</v>
       </c>
       <c r="Y10" s="1">
-        <v>36000</v>
+        <v>22500</v>
       </c>
       <c r="Z10" s="6" t="s">
         <v>54</v>
@@ -2028,7 +2033,7 @@
         <v>25000</v>
       </c>
       <c r="Y11" s="1">
-        <v>36000</v>
+        <v>27000</v>
       </c>
       <c r="Z11" s="7" t="s">
         <v>59</v>
@@ -2106,7 +2111,7 @@
         <v>30000</v>
       </c>
       <c r="Y12" s="1">
-        <v>36000</v>
+        <v>31500</v>
       </c>
       <c r="Z12" s="6" t="s">
         <v>63</v>
@@ -2518,7 +2523,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="T3 AA3 T4 AA4 T5 AA5 Z3:Z5 C3:S5 U3:V5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:V5 Z3:AA5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="89">
   <si>
     <t>#</t>
   </si>
@@ -249,10 +249,13 @@
     <t>炎魔领主</t>
   </si>
   <si>
-    <t>2E+16</t>
-  </si>
-  <si>
-    <t>1E+21</t>
+    <t>4E+7</t>
+  </si>
+  <si>
+    <t>1E+8</t>
+  </si>
+  <si>
+    <t>5E+11</t>
   </si>
   <si>
     <t>3002,3003</t>
@@ -261,28 +264,70 @@
     <t>冰霜巨龙</t>
   </si>
   <si>
+    <t>3E+8</t>
+  </si>
+  <si>
+    <t>2E+12</t>
+  </si>
+  <si>
     <t>2002,2003</t>
   </si>
   <si>
     <t>痛苦女王</t>
   </si>
   <si>
+    <t>23E+7</t>
+  </si>
+  <si>
+    <t>9E+8</t>
+  </si>
+  <si>
+    <t>8E+12</t>
+  </si>
+  <si>
     <t>1002,1003</t>
   </si>
   <si>
     <t>野蛮酋长</t>
   </si>
   <si>
+    <t>52E+7</t>
+  </si>
+  <si>
+    <t>27E+8</t>
+  </si>
+  <si>
+    <t>32E+12</t>
+  </si>
+  <si>
     <t>3002,3003,3004</t>
   </si>
   <si>
     <t>终末主宰</t>
   </si>
   <si>
+    <t>11E+8</t>
+  </si>
+  <si>
+    <t>9E+9</t>
+  </si>
+  <si>
+    <t>13E+13</t>
+  </si>
+  <si>
     <t>2002,2003,2004</t>
   </si>
   <si>
     <t>毁灭之王</t>
+  </si>
+  <si>
+    <t>25E+8</t>
+  </si>
+  <si>
+    <t>30E+9</t>
+  </si>
+  <si>
+    <t>55E+13</t>
   </si>
   <si>
     <t>1002,1003,1004</t>
@@ -476,7 +521,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -486,6 +531,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -806,7 +857,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -830,16 +881,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -848,89 +899,89 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -939,8 +990,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1605,7 +1658,7 @@
       <c r="I6" s="1">
         <v>10000</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J6" s="7" t="s">
         <v>40</v>
       </c>
       <c r="K6" s="1">
@@ -1679,25 +1732,31 @@
       <c r="I7" s="1">
         <v>100000</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="J7" s="7" t="s">
         <v>43</v>
       </c>
       <c r="K7" s="1">
+        <f t="shared" ref="K7:K17" si="0">K6+25</f>
         <v>75</v>
       </c>
       <c r="L7" s="1">
+        <f t="shared" ref="L7:L17" si="1">L6+15</f>
         <v>45</v>
       </c>
       <c r="M7" s="1">
-        <v>25</v>
+        <f t="shared" ref="M7:M17" si="2">M6+5</f>
+        <v>20</v>
       </c>
       <c r="N7" s="1">
-        <v>60</v>
-      </c>
-      <c r="O7" s="5">
+        <f t="shared" ref="N7:N17" si="3">N6+10</f>
+        <v>40</v>
+      </c>
+      <c r="O7" s="1">
+        <f t="shared" ref="O7:O17" si="4">O6+5</f>
         <v>15</v>
       </c>
-      <c r="P7" s="5">
+      <c r="P7" s="1">
+        <f t="shared" ref="P7:P17" si="5">P6+5</f>
         <v>25</v>
       </c>
       <c r="Q7" s="1">
@@ -1755,25 +1814,31 @@
       <c r="I8" s="1">
         <v>400000</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="J8" s="7" t="s">
         <v>46</v>
       </c>
       <c r="K8" s="1">
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="L8" s="1">
+        <f t="shared" si="1"/>
         <v>60</v>
       </c>
       <c r="M8" s="1">
-        <v>35</v>
+        <f t="shared" si="2"/>
+        <v>25</v>
       </c>
       <c r="N8" s="1">
-        <v>90</v>
-      </c>
-      <c r="O8" s="5">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="O8" s="1">
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="P8" s="2">
+      <c r="P8" s="1">
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="Q8" s="1">
@@ -1831,25 +1896,31 @@
       <c r="I9" s="1">
         <v>2000000</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="J9" s="7" t="s">
         <v>49</v>
       </c>
       <c r="K9" s="1">
+        <f t="shared" si="0"/>
         <v>125</v>
       </c>
       <c r="L9" s="1">
+        <f t="shared" si="1"/>
         <v>75</v>
       </c>
       <c r="M9" s="1">
-        <v>45</v>
+        <f t="shared" si="2"/>
+        <v>30</v>
       </c>
       <c r="N9" s="1">
-        <v>120</v>
-      </c>
-      <c r="O9" s="5">
+        <f t="shared" si="3"/>
+        <v>60</v>
+      </c>
+      <c r="O9" s="1">
+        <f t="shared" si="4"/>
         <v>25</v>
       </c>
-      <c r="P9" s="2">
+      <c r="P9" s="1">
+        <f t="shared" si="5"/>
         <v>35</v>
       </c>
       <c r="Q9" s="1">
@@ -1879,7 +1950,7 @@
       <c r="Y9" s="1">
         <v>18000</v>
       </c>
-      <c r="Z9" s="6" t="s">
+      <c r="Z9" s="7" t="s">
         <v>50</v>
       </c>
       <c r="AA9" s="1"/>
@@ -1906,28 +1977,34 @@
       <c r="H10" s="1">
         <v>7200000</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="J10" s="7" t="s">
         <v>53</v>
       </c>
       <c r="K10" s="1">
+        <f t="shared" si="0"/>
         <v>150</v>
       </c>
       <c r="L10" s="1">
+        <f t="shared" si="1"/>
         <v>90</v>
       </c>
       <c r="M10" s="1">
-        <v>60</v>
+        <f t="shared" si="2"/>
+        <v>35</v>
       </c>
       <c r="N10" s="1">
-        <v>150</v>
-      </c>
-      <c r="O10" s="5">
+        <f t="shared" si="3"/>
+        <v>70</v>
+      </c>
+      <c r="O10" s="1">
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
-      <c r="P10" s="2">
+      <c r="P10" s="1">
+        <f t="shared" si="5"/>
         <v>40</v>
       </c>
       <c r="Q10" s="1">
@@ -1957,7 +2034,7 @@
       <c r="Y10" s="1">
         <v>22500</v>
       </c>
-      <c r="Z10" s="6" t="s">
+      <c r="Z10" s="7" t="s">
         <v>54</v>
       </c>
       <c r="AA10" s="1"/>
@@ -1984,28 +2061,34 @@
       <c r="H11" s="1">
         <v>20000000</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="I11" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="J11" s="7" t="s">
         <v>58</v>
       </c>
       <c r="K11" s="1">
+        <f t="shared" si="0"/>
         <v>175</v>
       </c>
       <c r="L11" s="1">
+        <f t="shared" si="1"/>
         <v>105</v>
       </c>
       <c r="M11" s="1">
-        <v>75</v>
+        <f t="shared" si="2"/>
+        <v>40</v>
       </c>
       <c r="N11" s="1">
-        <v>180</v>
-      </c>
-      <c r="O11" s="5">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="O11" s="1">
+        <f t="shared" si="4"/>
         <v>35</v>
       </c>
-      <c r="P11" s="2">
+      <c r="P11" s="1">
+        <f t="shared" si="5"/>
         <v>45</v>
       </c>
       <c r="Q11" s="1">
@@ -2035,7 +2118,7 @@
       <c r="Y11" s="1">
         <v>27000</v>
       </c>
-      <c r="Z11" s="7" t="s">
+      <c r="Z11" s="8" t="s">
         <v>59</v>
       </c>
       <c r="AA11" s="1"/>
@@ -2059,32 +2142,38 @@
       <c r="G12" s="1">
         <v>7</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="H12" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="I12" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="J12" s="6" t="s">
+      <c r="I12" s="9" t="s">
         <v>62</v>
       </c>
+      <c r="J12" s="9" t="s">
+        <v>63</v>
+      </c>
       <c r="K12" s="1">
-        <v>150</v>
+        <f t="shared" si="0"/>
+        <v>200</v>
       </c>
       <c r="L12" s="1">
-        <v>60</v>
+        <f t="shared" si="1"/>
+        <v>120</v>
       </c>
       <c r="M12" s="1">
-        <v>35</v>
+        <f t="shared" si="2"/>
+        <v>45</v>
       </c>
       <c r="N12" s="1">
+        <f t="shared" si="3"/>
         <v>90</v>
       </c>
-      <c r="O12" s="5">
-        <v>20</v>
-      </c>
-      <c r="P12" s="2">
-        <v>30</v>
+      <c r="O12" s="1">
+        <f t="shared" si="4"/>
+        <v>40</v>
+      </c>
+      <c r="P12" s="1">
+        <f t="shared" si="5"/>
+        <v>50</v>
       </c>
       <c r="Q12" s="1">
         <v>0</v>
@@ -2113,8 +2202,8 @@
       <c r="Y12" s="1">
         <v>31500</v>
       </c>
-      <c r="Z12" s="6" t="s">
-        <v>63</v>
+      <c r="Z12" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="AA12" s="1"/>
       <c r="AB12" s="2" t="s">
@@ -2132,37 +2221,43 @@
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G13" s="1">
         <v>8</v>
       </c>
-      <c r="H13" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="J13" s="6" t="s">
+      <c r="H13" s="7" t="s">
         <v>62</v>
       </c>
+      <c r="I13" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>67</v>
+      </c>
       <c r="K13" s="1">
-        <v>150</v>
+        <f t="shared" si="0"/>
+        <v>225</v>
       </c>
       <c r="L13" s="1">
-        <v>60</v>
+        <f t="shared" si="1"/>
+        <v>135</v>
       </c>
       <c r="M13" s="1">
-        <v>35</v>
+        <f t="shared" si="2"/>
+        <v>50</v>
       </c>
       <c r="N13" s="1">
-        <v>90</v>
-      </c>
-      <c r="O13" s="5">
-        <v>20</v>
-      </c>
-      <c r="P13" s="2">
-        <v>30</v>
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+      <c r="O13" s="1">
+        <f t="shared" si="4"/>
+        <v>45</v>
+      </c>
+      <c r="P13" s="1">
+        <f t="shared" si="5"/>
+        <v>55</v>
       </c>
       <c r="Q13" s="1">
         <v>0</v>
@@ -2191,8 +2286,8 @@
       <c r="Y13" s="1">
         <v>36000</v>
       </c>
-      <c r="Z13" s="6" t="s">
-        <v>65</v>
+      <c r="Z13" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="AA13" s="1"/>
       <c r="AB13" s="2" t="s">
@@ -2210,37 +2305,43 @@
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G14" s="1">
         <v>9</v>
       </c>
-      <c r="H14" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>62</v>
+      <c r="H14" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>72</v>
       </c>
       <c r="K14" s="1">
+        <f t="shared" si="0"/>
+        <v>250</v>
+      </c>
+      <c r="L14" s="1">
+        <f t="shared" si="1"/>
         <v>150</v>
       </c>
-      <c r="L14" s="1">
+      <c r="M14" s="1">
+        <f t="shared" si="2"/>
+        <v>55</v>
+      </c>
+      <c r="N14" s="1">
+        <f t="shared" si="3"/>
+        <v>110</v>
+      </c>
+      <c r="O14" s="1">
+        <f t="shared" si="4"/>
+        <v>50</v>
+      </c>
+      <c r="P14" s="1">
+        <f t="shared" si="5"/>
         <v>60</v>
-      </c>
-      <c r="M14" s="1">
-        <v>35</v>
-      </c>
-      <c r="N14" s="1">
-        <v>90</v>
-      </c>
-      <c r="O14" s="5">
-        <v>20</v>
-      </c>
-      <c r="P14" s="2">
-        <v>30</v>
       </c>
       <c r="Q14" s="1">
         <v>0</v>
@@ -2269,8 +2370,8 @@
       <c r="Y14" s="1">
         <v>36000</v>
       </c>
-      <c r="Z14" s="7" t="s">
-        <v>67</v>
+      <c r="Z14" s="8" t="s">
+        <v>73</v>
       </c>
       <c r="AA14" s="1"/>
       <c r="AB14" s="2" t="s">
@@ -2288,37 +2389,43 @@
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G15" s="1">
         <v>10</v>
       </c>
-      <c r="H15" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>62</v>
+      <c r="H15" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>77</v>
       </c>
       <c r="K15" s="1">
-        <v>150</v>
+        <f t="shared" si="0"/>
+        <v>275</v>
       </c>
       <c r="L15" s="1">
+        <f t="shared" si="1"/>
+        <v>165</v>
+      </c>
+      <c r="M15" s="1">
+        <f t="shared" si="2"/>
         <v>60</v>
       </c>
-      <c r="M15" s="1">
-        <v>35</v>
-      </c>
       <c r="N15" s="1">
-        <v>90</v>
-      </c>
-      <c r="O15" s="5">
-        <v>20</v>
-      </c>
-      <c r="P15" s="2">
-        <v>30</v>
+        <f t="shared" si="3"/>
+        <v>120</v>
+      </c>
+      <c r="O15" s="1">
+        <f t="shared" si="4"/>
+        <v>55</v>
+      </c>
+      <c r="P15" s="1">
+        <f t="shared" si="5"/>
+        <v>65</v>
       </c>
       <c r="Q15" s="1">
         <v>0</v>
@@ -2347,8 +2454,8 @@
       <c r="Y15" s="1">
         <v>36000</v>
       </c>
-      <c r="Z15" s="6" t="s">
-        <v>69</v>
+      <c r="Z15" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="AA15" s="1"/>
       <c r="AB15" s="2" t="s">
@@ -2366,37 +2473,43 @@
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="G16" s="1">
         <v>11</v>
       </c>
-      <c r="H16" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>62</v>
+      <c r="H16" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>82</v>
       </c>
       <c r="K16" s="1">
-        <v>150</v>
+        <f t="shared" si="0"/>
+        <v>300</v>
       </c>
       <c r="L16" s="1">
+        <f t="shared" si="1"/>
+        <v>180</v>
+      </c>
+      <c r="M16" s="1">
+        <f t="shared" si="2"/>
+        <v>65</v>
+      </c>
+      <c r="N16" s="1">
+        <f t="shared" si="3"/>
+        <v>130</v>
+      </c>
+      <c r="O16" s="1">
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="M16" s="1">
-        <v>35</v>
-      </c>
-      <c r="N16" s="1">
-        <v>90</v>
-      </c>
-      <c r="O16" s="5">
-        <v>20</v>
-      </c>
-      <c r="P16" s="2">
-        <v>30</v>
+      <c r="P16" s="1">
+        <f t="shared" si="5"/>
+        <v>70</v>
       </c>
       <c r="Q16" s="1">
         <v>0</v>
@@ -2425,8 +2538,8 @@
       <c r="Y16" s="1">
         <v>36000</v>
       </c>
-      <c r="Z16" s="6" t="s">
-        <v>71</v>
+      <c r="Z16" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="AA16" s="1"/>
       <c r="AB16" s="2" t="s">
@@ -2444,37 +2557,43 @@
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="G17" s="1">
         <v>12</v>
       </c>
-      <c r="H17" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>62</v>
+      <c r="H17" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>87</v>
       </c>
       <c r="K17" s="1">
-        <v>150</v>
+        <f t="shared" si="0"/>
+        <v>325</v>
       </c>
       <c r="L17" s="1">
-        <v>60</v>
+        <f t="shared" si="1"/>
+        <v>195</v>
       </c>
       <c r="M17" s="1">
-        <v>35</v>
+        <f t="shared" si="2"/>
+        <v>70</v>
       </c>
       <c r="N17" s="1">
-        <v>90</v>
-      </c>
-      <c r="O17" s="5">
-        <v>20</v>
-      </c>
-      <c r="P17" s="2">
-        <v>30</v>
+        <f t="shared" si="3"/>
+        <v>140</v>
+      </c>
+      <c r="O17" s="1">
+        <f t="shared" si="4"/>
+        <v>65</v>
+      </c>
+      <c r="P17" s="1">
+        <f t="shared" si="5"/>
+        <v>75</v>
       </c>
       <c r="Q17" s="1">
         <v>0</v>
@@ -2503,8 +2622,8 @@
       <c r="Y17" s="1">
         <v>36000</v>
       </c>
-      <c r="Z17" s="7" t="s">
-        <v>73</v>
+      <c r="Z17" s="8" t="s">
+        <v>88</v>
       </c>
       <c r="AA17" s="1"/>
       <c r="AB17" s="2" t="s">
@@ -2523,7 +2642,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:V5 Z3:AA5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:J5 K3:V5 Z3:AA5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -2642,7 +2642,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:J5 K3:V5 Z3:AA5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:V5 Z3:AA5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="90">
   <si>
     <t>#</t>
   </si>
@@ -204,7 +204,7 @@
     <t>腐尸君主</t>
   </si>
   <si>
-    <t>10E+8</t>
+    <t>8E+8</t>
   </si>
   <si>
     <t>1小时</t>
@@ -213,7 +213,7 @@
     <t>梦魇鹿神</t>
   </si>
   <si>
-    <t>5E+9</t>
+    <t>4E+9</t>
   </si>
   <si>
     <t>3002</t>
@@ -240,7 +240,7 @@
     <t>3E+7</t>
   </si>
   <si>
-    <t>1E+11</t>
+    <t>8E+10</t>
   </si>
   <si>
     <t>1002</t>
@@ -249,13 +249,13 @@
     <t>炎魔领主</t>
   </si>
   <si>
-    <t>4E+7</t>
+    <t>28E+6</t>
   </si>
   <si>
     <t>1E+8</t>
   </si>
   <si>
-    <t>5E+11</t>
+    <t>3E+11</t>
   </si>
   <si>
     <t>3002,3003</t>
@@ -264,10 +264,13 @@
     <t>冰霜巨龙</t>
   </si>
   <si>
+    <t>57E+6</t>
+  </si>
+  <si>
     <t>3E+8</t>
   </si>
   <si>
-    <t>2E+12</t>
+    <t>12E+11</t>
   </si>
   <si>
     <t>2002,2003</t>
@@ -276,13 +279,13 @@
     <t>痛苦女王</t>
   </si>
   <si>
-    <t>23E+7</t>
+    <t>13E+7</t>
   </si>
   <si>
     <t>9E+8</t>
   </si>
   <si>
-    <t>8E+12</t>
+    <t>5E+12</t>
   </si>
   <si>
     <t>1002,1003</t>
@@ -291,13 +294,13 @@
     <t>野蛮酋长</t>
   </si>
   <si>
-    <t>52E+7</t>
+    <t>26E+7</t>
   </si>
   <si>
     <t>27E+8</t>
   </si>
   <si>
-    <t>32E+12</t>
+    <t>16E+12</t>
   </si>
   <si>
     <t>3002,3003,3004</t>
@@ -1653,7 +1656,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="1">
-        <v>10000</v>
+        <v>10500</v>
       </c>
       <c r="I6" s="1">
         <v>10000</v>
@@ -1727,7 +1730,7 @@
         <v>2</v>
       </c>
       <c r="H7" s="1">
-        <v>120000</v>
+        <v>110000</v>
       </c>
       <c r="I7" s="1">
         <v>100000</v>
@@ -1809,7 +1812,7 @@
         <v>3</v>
       </c>
       <c r="H8" s="1">
-        <v>800000</v>
+        <v>625000</v>
       </c>
       <c r="I8" s="1">
         <v>400000</v>
@@ -1891,7 +1894,7 @@
         <v>4</v>
       </c>
       <c r="H9" s="1">
-        <v>2400000</v>
+        <v>2050000</v>
       </c>
       <c r="I9" s="1">
         <v>2000000</v>
@@ -1975,7 +1978,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="1">
-        <v>7200000</v>
+        <v>5700000</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>40</v>
@@ -2059,7 +2062,7 @@
         <v>6</v>
       </c>
       <c r="H11" s="1">
-        <v>20000000</v>
+        <v>13000000</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>57</v>
@@ -2227,13 +2230,13 @@
         <v>8</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K13" s="1">
         <f t="shared" si="0"/>
@@ -2287,7 +2290,7 @@
         <v>36000</v>
       </c>
       <c r="Z13" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AA13" s="1"/>
       <c r="AB13" s="2" t="s">
@@ -2305,19 +2308,19 @@
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G14" s="1">
         <v>9</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K14" s="1">
         <f t="shared" si="0"/>
@@ -2371,7 +2374,7 @@
         <v>36000</v>
       </c>
       <c r="Z14" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AA14" s="1"/>
       <c r="AB14" s="2" t="s">
@@ -2389,19 +2392,19 @@
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G15" s="1">
         <v>10</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K15" s="1">
         <f t="shared" si="0"/>
@@ -2455,7 +2458,7 @@
         <v>36000</v>
       </c>
       <c r="Z15" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AA15" s="1"/>
       <c r="AB15" s="2" t="s">
@@ -2473,19 +2476,19 @@
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G16" s="1">
         <v>11</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K16" s="1">
         <f t="shared" si="0"/>
@@ -2539,7 +2542,7 @@
         <v>36000</v>
       </c>
       <c r="Z16" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AA16" s="1"/>
       <c r="AB16" s="2" t="s">
@@ -2557,19 +2560,19 @@
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G17" s="1">
         <v>12</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K17" s="1">
         <f t="shared" si="0"/>
@@ -2623,7 +2626,7 @@
         <v>36000</v>
       </c>
       <c r="Z17" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AA17" s="1"/>
       <c r="AB17" s="2" t="s">
@@ -2642,7 +2645,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:V5 Z3:AA5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:J5 K3:V5 Z3:AA5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -1787,7 +1787,7 @@
         <v>8000</v>
       </c>
       <c r="Y7" s="1">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="Z7" s="1"/>
       <c r="AA7" s="1"/>
@@ -1869,7 +1869,7 @@
         <v>10000</v>
       </c>
       <c r="Y8" s="1">
-        <v>13500</v>
+        <v>8000</v>
       </c>
       <c r="Z8" s="1"/>
       <c r="AA8" s="1"/>
@@ -1951,7 +1951,7 @@
         <v>15000</v>
       </c>
       <c r="Y9" s="1">
-        <v>18000</v>
+        <v>10000</v>
       </c>
       <c r="Z9" s="7" t="s">
         <v>50</v>
@@ -2035,7 +2035,7 @@
         <v>20000</v>
       </c>
       <c r="Y10" s="1">
-        <v>22500</v>
+        <v>12000</v>
       </c>
       <c r="Z10" s="7" t="s">
         <v>54</v>
@@ -2119,7 +2119,7 @@
         <v>25000</v>
       </c>
       <c r="Y11" s="1">
-        <v>27000</v>
+        <v>14000</v>
       </c>
       <c r="Z11" s="8" t="s">
         <v>59</v>
@@ -2203,7 +2203,7 @@
         <v>30000</v>
       </c>
       <c r="Y12" s="1">
-        <v>31500</v>
+        <v>16000</v>
       </c>
       <c r="Z12" s="7" t="s">
         <v>64</v>
@@ -2287,7 +2287,7 @@
         <v>40000</v>
       </c>
       <c r="Y13" s="1">
-        <v>36000</v>
+        <v>18000</v>
       </c>
       <c r="Z13" s="7" t="s">
         <v>69</v>
@@ -2371,7 +2371,7 @@
         <v>50000</v>
       </c>
       <c r="Y14" s="1">
-        <v>36000</v>
+        <v>18000</v>
       </c>
       <c r="Z14" s="8" t="s">
         <v>74</v>
@@ -2455,7 +2455,7 @@
         <v>60000</v>
       </c>
       <c r="Y15" s="1">
-        <v>36000</v>
+        <v>18000</v>
       </c>
       <c r="Z15" s="7" t="s">
         <v>79</v>
@@ -2539,7 +2539,7 @@
         <v>70000</v>
       </c>
       <c r="Y16" s="1">
-        <v>36000</v>
+        <v>18000</v>
       </c>
       <c r="Z16" s="7" t="s">
         <v>84</v>
@@ -2623,7 +2623,7 @@
         <v>80000</v>
       </c>
       <c r="Y17" s="1">
-        <v>36000</v>
+        <v>18000</v>
       </c>
       <c r="Z17" s="8" t="s">
         <v>89</v>
@@ -2645,7 +2645,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:J5 K3:V5 Z3:AA5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:V5 Z3:AA5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="87">
   <si>
     <t>#</t>
   </si>
@@ -249,7 +249,7 @@
     <t>炎魔领主</t>
   </si>
   <si>
-    <t>28E+6</t>
+    <t>9E+6</t>
   </si>
   <si>
     <t>1E+8</t>
@@ -264,7 +264,7 @@
     <t>冰霜巨龙</t>
   </si>
   <si>
-    <t>57E+6</t>
+    <t>2E+7</t>
   </si>
   <si>
     <t>3E+8</t>
@@ -279,7 +279,7 @@
     <t>痛苦女王</t>
   </si>
   <si>
-    <t>13E+7</t>
+    <t>5E+7</t>
   </si>
   <si>
     <t>9E+8</t>
@@ -294,9 +294,6 @@
     <t>野蛮酋长</t>
   </si>
   <si>
-    <t>26E+7</t>
-  </si>
-  <si>
     <t>27E+8</t>
   </si>
   <si>
@@ -309,9 +306,6 @@
     <t>终末主宰</t>
   </si>
   <si>
-    <t>11E+8</t>
-  </si>
-  <si>
     <t>9E+9</t>
   </si>
   <si>
@@ -322,9 +316,6 @@
   </si>
   <si>
     <t>毁灭之王</t>
-  </si>
-  <si>
-    <t>25E+8</t>
   </si>
   <si>
     <t>30E+9</t>
@@ -1730,7 +1721,7 @@
         <v>2</v>
       </c>
       <c r="H7" s="1">
-        <v>110000</v>
+        <v>70000</v>
       </c>
       <c r="I7" s="1">
         <v>100000</v>
@@ -1812,7 +1803,7 @@
         <v>3</v>
       </c>
       <c r="H8" s="1">
-        <v>625000</v>
+        <v>225000</v>
       </c>
       <c r="I8" s="1">
         <v>400000</v>
@@ -1894,7 +1885,7 @@
         <v>4</v>
       </c>
       <c r="H9" s="1">
-        <v>2050000</v>
+        <v>850000</v>
       </c>
       <c r="I9" s="1">
         <v>2000000</v>
@@ -1978,7 +1969,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="1">
-        <v>5700000</v>
+        <v>1000000</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>40</v>
@@ -2062,7 +2053,7 @@
         <v>6</v>
       </c>
       <c r="H11" s="1">
-        <v>13000000</v>
+        <v>3000000</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>57</v>
@@ -2398,13 +2389,13 @@
         <v>10</v>
       </c>
       <c r="H15" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="I15" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I15" s="7" t="s">
+      <c r="J15" s="7" t="s">
         <v>77</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>78</v>
       </c>
       <c r="K15" s="1">
         <f t="shared" si="0"/>
@@ -2458,7 +2449,7 @@
         <v>18000</v>
       </c>
       <c r="Z15" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AA15" s="1"/>
       <c r="AB15" s="2" t="s">
@@ -2476,19 +2467,19 @@
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G16" s="1">
         <v>11</v>
       </c>
       <c r="H16" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J16" s="7" t="s">
         <v>81</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>83</v>
       </c>
       <c r="K16" s="1">
         <f t="shared" si="0"/>
@@ -2542,7 +2533,7 @@
         <v>18000</v>
       </c>
       <c r="Z16" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AA16" s="1"/>
       <c r="AB16" s="2" t="s">
@@ -2560,19 +2551,19 @@
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G17" s="1">
         <v>12</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K17" s="1">
         <f t="shared" si="0"/>
@@ -2626,7 +2617,7 @@
         <v>18000</v>
       </c>
       <c r="Z17" s="8" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="AA17" s="1"/>
       <c r="AB17" s="2" t="s">
